--- a/files/九龙-启德-启德海湾 1.xlsx
+++ b/files/九龙-启德-启德海湾 1.xlsx
@@ -38860,38 +38860,30 @@
       </c>
       <c r="F614" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G614" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H614" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I614" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="H614" s="5" t="n">
+        <v>9928000</v>
+      </c>
+      <c r="I614" s="5" t="n">
+        <v>20813</v>
       </c>
       <c r="J614" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K614" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L614" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K614" s="5" t="n">
+        <v>9928000</v>
+      </c>
+      <c r="L614" s="5" t="n">
+        <v>20813</v>
       </c>
       <c r="M614" s="3" t="inlineStr">
         <is>
@@ -38900,7 +38892,7 @@
       </c>
       <c r="N614" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -67822,7 +67814,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -67832,7 +67824,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>233</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -69824,12 +69816,12 @@
 (25年-11月-21日)</t>
         </is>
       </c>
-      <c r="E29" s="20" t="inlineStr">
+      <c r="E29" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
-招标单位
--
-(在售)</t>
+$993万
+$20,813/呎
+(26年-09月-06日)</t>
         </is>
       </c>
       <c r="F29" s="21" t="inlineStr">

--- a/files/九龙-启德-启德海湾 1.xlsx
+++ b/files/九龙-启德-启德海湾 1.xlsx
@@ -5822,7 +5822,7 @@
         </is>
       </c>
       <c r="E83" s="4" t="n">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>8899000</v>
       </c>
       <c r="I83" s="5" t="n">
-        <v>20695</v>
+        <v>20744</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>8899000</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>20695</v>
+        <v>20744</v>
       </c>
       <c r="M83" s="3" t="inlineStr">
         <is>
@@ -22842,7 +22842,7 @@
         </is>
       </c>
       <c r="E357" s="4" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F357" s="3" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>5020000</v>
       </c>
       <c r="I357" s="5" t="n">
-        <v>16299</v>
+        <v>16246</v>
       </c>
       <c r="J357" s="3" t="inlineStr">
         <is>
@@ -22869,7 +22869,7 @@
         <v>5020000</v>
       </c>
       <c r="L357" s="5" t="n">
-        <v>16299</v>
+        <v>16246</v>
       </c>
       <c r="M357" s="3" t="inlineStr">
         <is>
@@ -65161,9 +65161,9 @@
       </c>
       <c r="L11" s="21" t="inlineStr">
         <is>
-          <t>L | 430呎 (2房)
+          <t>L | 429呎 (2房)
 $890万
-$20,695/呎
+$20,744/呎
 (24年-06月-24日)</t>
         </is>
       </c>
@@ -67484,9 +67484,9 @@
       </c>
       <c r="K32" s="21" t="inlineStr">
         <is>
-          <t>K | 308呎 (1房)
+          <t>K | 309呎 (1房)
 $502万
-$16,299/呎
+$16,246/呎
 (24年-12月-30日)</t>
         </is>
       </c>

--- a/files/九龙-启德-启德海湾 1.xlsx
+++ b/files/九龙-启德-启德海湾 1.xlsx
@@ -16448,7 +16448,7 @@
         </is>
       </c>
       <c r="E254" s="4" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F254" s="3" t="inlineStr">
         <is>
@@ -16464,7 +16464,7 @@
         <v>5218000</v>
       </c>
       <c r="I254" s="5" t="n">
-        <v>17108</v>
+        <v>17052</v>
       </c>
       <c r="J254" s="3" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>5218000</v>
       </c>
       <c r="L254" s="5" t="n">
-        <v>17108</v>
+        <v>17052</v>
       </c>
       <c r="M254" s="3" t="inlineStr">
         <is>
@@ -66588,9 +66588,9 @@
       </c>
       <c r="J24" s="21" t="inlineStr">
         <is>
-          <t>J | 305呎 (1房)
+          <t>J | 306呎 (1房)
 $522万
-$17,108/呎
+$17,052/呎
 (25年-03月-06日)</t>
         </is>
       </c>

--- a/files/九龙-启德-启德海湾 1.xlsx
+++ b/files/九龙-启德-启德海湾 1.xlsx
@@ -3521,7 +3521,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -11604,7 +11604,7 @@
         </is>
       </c>
       <c r="E176" s="4" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
@@ -11620,7 +11620,7 @@
         <v>5367000</v>
       </c>
       <c r="I176" s="5" t="n">
-        <v>17597</v>
+        <v>17539</v>
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>5367000</v>
       </c>
       <c r="L176" s="5" t="n">
-        <v>17597</v>
+        <v>17539</v>
       </c>
       <c r="M176" s="3" t="inlineStr">
         <is>
@@ -64815,7 +64815,7 @@
           <t>J | 306呎 (1房)
 $729万
 $23,817/呎
-(26年-08月-19日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="K8" s="21" t="inlineStr">
@@ -65922,9 +65922,9 @@
       </c>
       <c r="J18" s="21" t="inlineStr">
         <is>
-          <t>J | 305呎 (1房)
+          <t>J | 306呎 (1房)
 $537万
-$17,597/呎
+$17,539/呎
 (25年-03月-25日)</t>
         </is>
       </c>

--- a/files/九龙-启德-启德海湾 1.xlsx
+++ b/files/九龙-启德-启德海湾 1.xlsx
@@ -19556,7 +19556,7 @@
         </is>
       </c>
       <c r="E304" s="4" t="n">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F304" s="3" t="inlineStr">
         <is>
@@ -19572,7 +19572,7 @@
         <v>8480000</v>
       </c>
       <c r="I304" s="5" t="n">
-        <v>19721</v>
+        <v>19767</v>
       </c>
       <c r="J304" s="3" t="inlineStr">
         <is>
@@ -19583,7 +19583,7 @@
         <v>8480000</v>
       </c>
       <c r="L304" s="5" t="n">
-        <v>19721</v>
+        <v>19767</v>
       </c>
       <c r="M304" s="3" t="inlineStr">
         <is>
@@ -67048,9 +67048,9 @@
       </c>
       <c r="L28" s="21" t="inlineStr">
         <is>
-          <t>L | 430呎 (2房)
+          <t>L | 429呎 (2房)
 $848万
-$19,721/呎
+$19,767/呎
 (23年-11月-20日)</t>
         </is>
       </c>

--- a/files/九龙-启德-启德海湾 1.xlsx
+++ b/files/九龙-启德-启德海湾 1.xlsx
@@ -20486,7 +20486,7 @@
         </is>
       </c>
       <c r="E319" s="4" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F319" s="3" t="inlineStr">
         <is>
@@ -20502,7 +20502,7 @@
         <v>5138000</v>
       </c>
       <c r="I319" s="5" t="n">
-        <v>16846</v>
+        <v>16791</v>
       </c>
       <c r="J319" s="3" t="inlineStr">
         <is>
@@ -20513,7 +20513,7 @@
         <v>5138000</v>
       </c>
       <c r="L319" s="5" t="n">
-        <v>16846</v>
+        <v>16791</v>
       </c>
       <c r="M319" s="3" t="inlineStr">
         <is>
@@ -38865,7 +38865,7 @@
       </c>
       <c r="G614" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H614" s="5" t="n">
@@ -67143,9 +67143,9 @@
       </c>
       <c r="J29" s="21" t="inlineStr">
         <is>
-          <t>J | 305呎 (1房)
+          <t>J | 306呎 (1房)
 $514万
-$16,846/呎
+$16,791/呎
 (25年-03月-14日)</t>
         </is>
       </c>
@@ -69821,7 +69821,7 @@
           <t>D | 477呎 (2房)
 $993万
 $20,813/呎
-(26年-09月-06日)</t>
+(26年-10月-02日)</t>
         </is>
       </c>
       <c r="F29" s="21" t="inlineStr">

--- a/files/九龙-启德-启德海湾 1.xlsx
+++ b/files/九龙-启德-启德海湾 1.xlsx
@@ -39166,7 +39166,7 @@
         </is>
       </c>
       <c r="E619" s="4" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F619" s="3" t="inlineStr">
         <is>
@@ -39182,7 +39182,7 @@
         <v>6993000</v>
       </c>
       <c r="I619" s="5" t="n">
-        <v>16225</v>
+        <v>16188</v>
       </c>
       <c r="J619" s="3" t="inlineStr">
         <is>
@@ -39193,7 +39193,7 @@
         <v>6993000</v>
       </c>
       <c r="L619" s="5" t="n">
-        <v>16225</v>
+        <v>16188</v>
       </c>
       <c r="M619" s="3" t="inlineStr">
         <is>
@@ -69929,9 +69929,9 @@
       </c>
       <c r="I30" s="21" t="inlineStr">
         <is>
-          <t>H | 431呎 (2房)
+          <t>H | 432呎 (2房)
 $699万
-$16,225/呎
+$16,188/呎
 (24年-10月-14日)</t>
         </is>
       </c>

--- a/files/九龙-启德-启德海湾 1.xlsx
+++ b/files/九龙-启德-启德海湾 1.xlsx
@@ -13588,7 +13588,7 @@
         </is>
       </c>
       <c r="E208" s="4" t="n">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F208" s="3" t="inlineStr">
         <is>
@@ -66096,7 +66096,7 @@
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>C | 498呎 (2房)
+          <t>C | 497呎 (2房)
 招标单位
 -
 (在售)</t>

--- a/files/九龙-启德-启德海湾 1.xlsx
+++ b/files/九龙-启德-启德海湾 1.xlsx
@@ -3202,7 +3202,7 @@
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
@@ -3218,7 +3218,7 @@
         <v>21438000</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>27698</v>
+        <v>27805</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         <v>21438000</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>27698</v>
+        <v>27805</v>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>6528000</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>21126</v>
+        <v>21195</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         <v>6528000</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>21126</v>
+        <v>21195</v>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>7288000</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>23817</v>
+        <v>23895</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>7288000</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>23817</v>
+        <v>23895</v>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>6348000</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>20745</v>
+        <v>20813</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>6348000</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>20745</v>
+        <v>20813</v>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>6455000</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>20890</v>
+        <v>20958</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>6455000</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>20890</v>
+        <v>20958</v>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>7218000</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>23588</v>
+        <v>23666</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>7218000</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>23588</v>
+        <v>23666</v>
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>6318000</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>20647</v>
+        <v>20715</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>6318000</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>20647</v>
+        <v>20715</v>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>20068000</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>25928</v>
+        <v>26029</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>20068000</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>25928</v>
+        <v>26029</v>
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>6720000</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>23579</v>
+        <v>23333</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>6720000</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>23579</v>
+        <v>23333</v>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="E71" s="4" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>6154000</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>19916</v>
+        <v>19981</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>6154000</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>19916</v>
+        <v>19981</v>
       </c>
       <c r="M71" s="3" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
         <v>6956000</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>22732</v>
+        <v>22807</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         <v>6956000</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>22732</v>
+        <v>22807</v>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="E81" s="4" t="n">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         <v>6788000</v>
       </c>
       <c r="I81" s="5" t="n">
-        <v>23818</v>
+        <v>23569</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>6788000</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>23818</v>
+        <v>23569</v>
       </c>
       <c r="M81" s="3" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         </is>
       </c>
       <c r="E83" s="4" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>8899000</v>
       </c>
       <c r="I83" s="5" t="n">
-        <v>20744</v>
+        <v>20695</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>8899000</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>20744</v>
+        <v>20695</v>
       </c>
       <c r="M83" s="3" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         </is>
       </c>
       <c r="E84" s="4" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>6133000</v>
       </c>
       <c r="I84" s="5" t="n">
-        <v>19848</v>
+        <v>19912</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>6133000</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>19848</v>
+        <v>19912</v>
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         </is>
       </c>
       <c r="E85" s="4" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
@@ -5962,7 +5962,7 @@
         <v>6890000</v>
       </c>
       <c r="I85" s="5" t="n">
-        <v>22516</v>
+        <v>22590</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
         <v>6890000</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>22516</v>
+        <v>22590</v>
       </c>
       <c r="M85" s="3" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         </is>
       </c>
       <c r="E86" s="4" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>6268000</v>
       </c>
       <c r="I86" s="5" t="n">
-        <v>20484</v>
+        <v>20551</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
         <v>6268000</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>20484</v>
+        <v>20551</v>
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         </is>
       </c>
       <c r="E93" s="4" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>18888000</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>24403</v>
+        <v>24498</v>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>18888000</v>
       </c>
       <c r="L93" s="5" t="n">
-        <v>24403</v>
+        <v>24498</v>
       </c>
       <c r="M93" s="3" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         </is>
       </c>
       <c r="E94" s="4" t="n">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
@@ -6520,7 +6520,7 @@
         <v>6720000</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>23579</v>
+        <v>23333</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         <v>6720000</v>
       </c>
       <c r="L94" s="5" t="n">
-        <v>23579</v>
+        <v>23333</v>
       </c>
       <c r="M94" s="3" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         </is>
       </c>
       <c r="E99" s="4" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>6200000</v>
       </c>
       <c r="I99" s="5" t="n">
-        <v>20261</v>
+        <v>20328</v>
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
         <v>6200000</v>
       </c>
       <c r="L99" s="5" t="n">
-        <v>20261</v>
+        <v>20328</v>
       </c>
       <c r="M99" s="3" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         </is>
       </c>
       <c r="E107" s="4" t="n">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>6308000</v>
       </c>
       <c r="I107" s="5" t="n">
-        <v>22133</v>
+        <v>21903</v>
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         <v>6308000</v>
       </c>
       <c r="L107" s="5" t="n">
-        <v>22133</v>
+        <v>21903</v>
       </c>
       <c r="M107" s="3" t="inlineStr">
         <is>
@@ -7628,7 +7628,7 @@
         </is>
       </c>
       <c r="E112" s="4" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
@@ -7644,7 +7644,7 @@
         <v>5958000</v>
       </c>
       <c r="I112" s="5" t="n">
-        <v>19471</v>
+        <v>19534</v>
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>5958000</v>
       </c>
       <c r="L112" s="5" t="n">
-        <v>19471</v>
+        <v>19534</v>
       </c>
       <c r="M112" s="3" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
         </is>
       </c>
       <c r="E125" s="4" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         <v>5921000</v>
       </c>
       <c r="I125" s="5" t="n">
-        <v>19350</v>
+        <v>19413</v>
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>5921000</v>
       </c>
       <c r="L125" s="5" t="n">
-        <v>19350</v>
+        <v>19413</v>
       </c>
       <c r="M125" s="3" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         </is>
       </c>
       <c r="E132" s="4" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
@@ -8884,7 +8884,7 @@
         <v>18068000</v>
       </c>
       <c r="I132" s="5" t="n">
-        <v>23344</v>
+        <v>23435</v>
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
@@ -8895,7 +8895,7 @@
         <v>18068000</v>
       </c>
       <c r="L132" s="5" t="n">
-        <v>23344</v>
+        <v>23435</v>
       </c>
       <c r="M132" s="3" t="inlineStr">
         <is>
@@ -9116,7 +9116,7 @@
         </is>
       </c>
       <c r="E136" s="4" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
@@ -9132,7 +9132,7 @@
         <v>5989000</v>
       </c>
       <c r="I136" s="5" t="n">
-        <v>19382</v>
+        <v>19445</v>
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
         <v>5989000</v>
       </c>
       <c r="L136" s="5" t="n">
-        <v>19382</v>
+        <v>19445</v>
       </c>
       <c r="M136" s="3" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         </is>
       </c>
       <c r="E145" s="4" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         <v>17553800</v>
       </c>
       <c r="I145" s="5" t="n">
-        <v>22679</v>
+        <v>22768</v>
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
@@ -9701,7 +9701,7 @@
         <v>17553800</v>
       </c>
       <c r="L145" s="5" t="n">
-        <v>22679</v>
+        <v>22768</v>
       </c>
       <c r="M145" s="3" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
         </is>
       </c>
       <c r="E146" s="4" t="n">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         <v>5982000</v>
       </c>
       <c r="I146" s="5" t="n">
-        <v>20989</v>
+        <v>20771</v>
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
         <v>5982000</v>
       </c>
       <c r="L146" s="5" t="n">
-        <v>20989</v>
+        <v>20771</v>
       </c>
       <c r="M146" s="3" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         </is>
       </c>
       <c r="E158" s="4" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
         <v>19668000</v>
       </c>
       <c r="I158" s="5" t="n">
-        <v>25411</v>
+        <v>25510</v>
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
@@ -10515,7 +10515,7 @@
         <v>19668000</v>
       </c>
       <c r="L158" s="5" t="n">
-        <v>25411</v>
+        <v>25510</v>
       </c>
       <c r="M158" s="3" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         </is>
       </c>
       <c r="E159" s="4" t="n">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
@@ -10566,7 +10566,7 @@
         <v>5943000</v>
       </c>
       <c r="I159" s="5" t="n">
-        <v>20853</v>
+        <v>20635</v>
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
@@ -10577,7 +10577,7 @@
         <v>5943000</v>
       </c>
       <c r="L159" s="5" t="n">
-        <v>20853</v>
+        <v>20635</v>
       </c>
       <c r="M159" s="3" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
         </is>
       </c>
       <c r="E162" s="4" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
@@ -10752,7 +10752,7 @@
         <v>5921000</v>
       </c>
       <c r="I162" s="5" t="n">
-        <v>19162</v>
+        <v>19224</v>
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
@@ -10763,7 +10763,7 @@
         <v>5921000</v>
       </c>
       <c r="L162" s="5" t="n">
-        <v>19162</v>
+        <v>19224</v>
       </c>
       <c r="M162" s="3" t="inlineStr">
         <is>
@@ -11294,7 +11294,7 @@
         </is>
       </c>
       <c r="E171" s="4" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
         <v>17738000</v>
       </c>
       <c r="I171" s="5" t="n">
-        <v>22917</v>
+        <v>23006</v>
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
@@ -11321,7 +11321,7 @@
         <v>17738000</v>
       </c>
       <c r="L171" s="5" t="n">
-        <v>22917</v>
+        <v>23006</v>
       </c>
       <c r="M171" s="3" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         </is>
       </c>
       <c r="E172" s="4" t="n">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
@@ -11372,7 +11372,7 @@
         <v>5486000</v>
       </c>
       <c r="I172" s="5" t="n">
-        <v>19249</v>
+        <v>19049</v>
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>5486000</v>
       </c>
       <c r="L172" s="5" t="n">
-        <v>19249</v>
+        <v>19049</v>
       </c>
       <c r="M172" s="3" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         </is>
       </c>
       <c r="E176" s="4" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
@@ -11620,7 +11620,7 @@
         <v>5367000</v>
       </c>
       <c r="I176" s="5" t="n">
-        <v>17539</v>
+        <v>17597</v>
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>5367000</v>
       </c>
       <c r="L176" s="5" t="n">
-        <v>17539</v>
+        <v>17597</v>
       </c>
       <c r="M176" s="3" t="inlineStr">
         <is>
@@ -12906,7 +12906,7 @@
         </is>
       </c>
       <c r="E197" s="4" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
@@ -12922,7 +12922,7 @@
         <v>18508000</v>
       </c>
       <c r="I197" s="5" t="n">
-        <v>23912</v>
+        <v>24005</v>
       </c>
       <c r="J197" s="3" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>18508000</v>
       </c>
       <c r="L197" s="5" t="n">
-        <v>23912</v>
+        <v>24005</v>
       </c>
       <c r="M197" s="3" t="inlineStr">
         <is>
@@ -13588,7 +13588,7 @@
         </is>
       </c>
       <c r="E208" s="4" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F208" s="3" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         </is>
       </c>
       <c r="E210" s="4" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
@@ -13736,7 +13736,7 @@
         <v>18880000</v>
       </c>
       <c r="I210" s="5" t="n">
-        <v>24393</v>
+        <v>24488</v>
       </c>
       <c r="J210" s="3" t="inlineStr">
         <is>
@@ -13747,7 +13747,7 @@
         <v>18880000</v>
       </c>
       <c r="L210" s="5" t="n">
-        <v>24393</v>
+        <v>24488</v>
       </c>
       <c r="M210" s="3" t="inlineStr">
         <is>
@@ -14402,7 +14402,7 @@
         </is>
       </c>
       <c r="E221" s="4" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>11428000</v>
       </c>
       <c r="I221" s="5" t="n">
-        <v>22994</v>
+        <v>22948</v>
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
@@ -14429,7 +14429,7 @@
         <v>11428000</v>
       </c>
       <c r="L221" s="5" t="n">
-        <v>22994</v>
+        <v>22948</v>
       </c>
       <c r="M221" s="3" t="inlineStr">
         <is>
@@ -14588,7 +14588,7 @@
         </is>
       </c>
       <c r="E224" s="4" t="n">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
@@ -14604,7 +14604,7 @@
         <v>4834000</v>
       </c>
       <c r="I224" s="5" t="n">
-        <v>16961</v>
+        <v>16785</v>
       </c>
       <c r="J224" s="3" t="inlineStr">
         <is>
@@ -14615,7 +14615,7 @@
         <v>4834000</v>
       </c>
       <c r="L224" s="5" t="n">
-        <v>16961</v>
+        <v>16785</v>
       </c>
       <c r="M224" s="3" t="inlineStr">
         <is>
@@ -16014,7 +16014,7 @@
         </is>
       </c>
       <c r="E247" s="4" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F247" s="3" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>10808000</v>
       </c>
       <c r="I247" s="5" t="n">
-        <v>21746</v>
+        <v>21703</v>
       </c>
       <c r="J247" s="3" t="inlineStr">
         <is>
@@ -16041,7 +16041,7 @@
         <v>10808000</v>
       </c>
       <c r="L247" s="5" t="n">
-        <v>21746</v>
+        <v>21703</v>
       </c>
       <c r="M247" s="3" t="inlineStr">
         <is>
@@ -16448,7 +16448,7 @@
         </is>
       </c>
       <c r="E254" s="4" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F254" s="3" t="inlineStr">
         <is>
@@ -16464,7 +16464,7 @@
         <v>5218000</v>
       </c>
       <c r="I254" s="5" t="n">
-        <v>17052</v>
+        <v>17108</v>
       </c>
       <c r="J254" s="3" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>5218000</v>
       </c>
       <c r="L254" s="5" t="n">
-        <v>17052</v>
+        <v>17108</v>
       </c>
       <c r="M254" s="3" t="inlineStr">
         <is>
@@ -17262,7 +17262,7 @@
         </is>
       </c>
       <c r="E267" s="4" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F267" s="3" t="inlineStr">
         <is>
@@ -17278,7 +17278,7 @@
         <v>5242000</v>
       </c>
       <c r="I267" s="5" t="n">
-        <v>17131</v>
+        <v>17187</v>
       </c>
       <c r="J267" s="3" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>5242000</v>
       </c>
       <c r="L267" s="5" t="n">
-        <v>17131</v>
+        <v>17187</v>
       </c>
       <c r="M267" s="3" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         </is>
       </c>
       <c r="E273" s="4" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F273" s="3" t="inlineStr">
         <is>
@@ -17650,7 +17650,7 @@
         <v>10708000</v>
       </c>
       <c r="I273" s="5" t="n">
-        <v>21545</v>
+        <v>21502</v>
       </c>
       <c r="J273" s="3" t="inlineStr">
         <is>
@@ -17661,7 +17661,7 @@
         <v>10708000</v>
       </c>
       <c r="L273" s="5" t="n">
-        <v>21545</v>
+        <v>21502</v>
       </c>
       <c r="M273" s="3" t="inlineStr">
         <is>
@@ -17758,7 +17758,7 @@
         </is>
       </c>
       <c r="E275" s="4" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="F275" s="3" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>17588000</v>
       </c>
       <c r="I275" s="5" t="n">
-        <v>22724</v>
+        <v>22812</v>
       </c>
       <c r="J275" s="3" t="inlineStr">
         <is>
@@ -17785,7 +17785,7 @@
         <v>17588000</v>
       </c>
       <c r="L275" s="5" t="n">
-        <v>22724</v>
+        <v>22812</v>
       </c>
       <c r="M275" s="3" t="inlineStr">
         <is>
@@ -18626,7 +18626,7 @@
         </is>
       </c>
       <c r="E289" s="4" t="n">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F289" s="3" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
         <v>4760000</v>
       </c>
       <c r="I289" s="5" t="n">
-        <v>16702</v>
+        <v>16528</v>
       </c>
       <c r="J289" s="3" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>4760000</v>
       </c>
       <c r="L289" s="5" t="n">
-        <v>16702</v>
+        <v>16528</v>
       </c>
       <c r="M289" s="3" t="inlineStr">
         <is>
@@ -18750,7 +18750,7 @@
         </is>
       </c>
       <c r="E291" s="4" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F291" s="3" t="inlineStr">
         <is>
@@ -18766,7 +18766,7 @@
         <v>8608000</v>
       </c>
       <c r="I291" s="5" t="n">
-        <v>20065</v>
+        <v>20019</v>
       </c>
       <c r="J291" s="3" t="inlineStr">
         <is>
@@ -18777,7 +18777,7 @@
         <v>8608000</v>
       </c>
       <c r="L291" s="5" t="n">
-        <v>20065</v>
+        <v>20019</v>
       </c>
       <c r="M291" s="3" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         </is>
       </c>
       <c r="E301" s="4" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="F301" s="3" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>16968000</v>
       </c>
       <c r="I301" s="5" t="n">
-        <v>21922</v>
+        <v>22008</v>
       </c>
       <c r="J301" s="3" t="inlineStr">
         <is>
@@ -19397,7 +19397,7 @@
         <v>16968000</v>
       </c>
       <c r="L301" s="5" t="n">
-        <v>21922</v>
+        <v>22008</v>
       </c>
       <c r="M301" s="3" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         </is>
       </c>
       <c r="E304" s="4" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F304" s="3" t="inlineStr">
         <is>
@@ -19572,7 +19572,7 @@
         <v>8480000</v>
       </c>
       <c r="I304" s="5" t="n">
-        <v>19767</v>
+        <v>19721</v>
       </c>
       <c r="J304" s="3" t="inlineStr">
         <is>
@@ -19583,7 +19583,7 @@
         <v>8480000</v>
       </c>
       <c r="L304" s="5" t="n">
-        <v>19767</v>
+        <v>19721</v>
       </c>
       <c r="M304" s="3" t="inlineStr">
         <is>
@@ -19680,7 +19680,7 @@
         </is>
       </c>
       <c r="E306" s="4" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F306" s="3" t="inlineStr">
         <is>
@@ -19696,7 +19696,7 @@
         <v>5917000</v>
       </c>
       <c r="I306" s="5" t="n">
-        <v>19337</v>
+        <v>19400</v>
       </c>
       <c r="J306" s="3" t="inlineStr">
         <is>
@@ -19707,7 +19707,7 @@
         <v>5917000</v>
       </c>
       <c r="L306" s="5" t="n">
-        <v>19337</v>
+        <v>19400</v>
       </c>
       <c r="M306" s="3" t="inlineStr">
         <is>
@@ -20052,7 +20052,7 @@
         </is>
       </c>
       <c r="E312" s="4" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F312" s="3" t="inlineStr">
         <is>
@@ -20068,7 +20068,7 @@
         <v>10008000</v>
       </c>
       <c r="I312" s="5" t="n">
-        <v>20137</v>
+        <v>20096</v>
       </c>
       <c r="J312" s="3" t="inlineStr">
         <is>
@@ -20079,7 +20079,7 @@
         <v>10008000</v>
       </c>
       <c r="L312" s="5" t="n">
-        <v>20137</v>
+        <v>20096</v>
       </c>
       <c r="M312" s="3" t="inlineStr">
         <is>
@@ -20486,7 +20486,7 @@
         </is>
       </c>
       <c r="E319" s="4" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F319" s="3" t="inlineStr">
         <is>
@@ -20502,7 +20502,7 @@
         <v>5138000</v>
       </c>
       <c r="I319" s="5" t="n">
-        <v>16791</v>
+        <v>16846</v>
       </c>
       <c r="J319" s="3" t="inlineStr">
         <is>
@@ -20513,7 +20513,7 @@
         <v>5138000</v>
       </c>
       <c r="L319" s="5" t="n">
-        <v>16791</v>
+        <v>16846</v>
       </c>
       <c r="M319" s="3" t="inlineStr">
         <is>
@@ -21788,7 +21788,7 @@
         </is>
       </c>
       <c r="E340" s="4" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="F340" s="3" t="inlineStr">
         <is>
@@ -21804,7 +21804,7 @@
         <v>16610000</v>
       </c>
       <c r="I340" s="5" t="n">
-        <v>21460</v>
+        <v>21543</v>
       </c>
       <c r="J340" s="3" t="inlineStr">
         <is>
@@ -21815,7 +21815,7 @@
         <v>16610000</v>
       </c>
       <c r="L340" s="5" t="n">
-        <v>21460</v>
+        <v>21543</v>
       </c>
       <c r="M340" s="3" t="inlineStr">
         <is>
@@ -22470,7 +22470,7 @@
         </is>
       </c>
       <c r="E351" s="4" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F351" s="3" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>9988000</v>
       </c>
       <c r="I351" s="5" t="n">
-        <v>20097</v>
+        <v>20056</v>
       </c>
       <c r="J351" s="3" t="inlineStr">
         <is>
@@ -22497,7 +22497,7 @@
         <v>9988000</v>
       </c>
       <c r="L351" s="5" t="n">
-        <v>20097</v>
+        <v>20056</v>
       </c>
       <c r="M351" s="3" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         </is>
       </c>
       <c r="E354" s="4" t="n">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F354" s="3" t="inlineStr">
         <is>
@@ -22672,7 +22672,7 @@
         <v>4674000</v>
       </c>
       <c r="I354" s="5" t="n">
-        <v>16400</v>
+        <v>16229</v>
       </c>
       <c r="J354" s="3" t="inlineStr">
         <is>
@@ -22683,7 +22683,7 @@
         <v>4674000</v>
       </c>
       <c r="L354" s="5" t="n">
-        <v>16400</v>
+        <v>16229</v>
       </c>
       <c r="M354" s="3" t="inlineStr">
         <is>
@@ -22842,7 +22842,7 @@
         </is>
       </c>
       <c r="E357" s="4" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F357" s="3" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>5020000</v>
       </c>
       <c r="I357" s="5" t="n">
-        <v>16246</v>
+        <v>16299</v>
       </c>
       <c r="J357" s="3" t="inlineStr">
         <is>
@@ -22869,7 +22869,7 @@
         <v>5020000</v>
       </c>
       <c r="L357" s="5" t="n">
-        <v>16246</v>
+        <v>16299</v>
       </c>
       <c r="M357" s="3" t="inlineStr">
         <is>
@@ -23276,7 +23276,7 @@
         </is>
       </c>
       <c r="E364" s="4" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F364" s="3" t="inlineStr">
         <is>
@@ -23292,7 +23292,7 @@
         <v>9738000</v>
       </c>
       <c r="I364" s="5" t="n">
-        <v>19594</v>
+        <v>19554</v>
       </c>
       <c r="J364" s="3" t="inlineStr">
         <is>
@@ -23303,7 +23303,7 @@
         <v>9738000</v>
       </c>
       <c r="L364" s="5" t="n">
-        <v>19594</v>
+        <v>19554</v>
       </c>
       <c r="M364" s="3" t="inlineStr">
         <is>
@@ -23400,7 +23400,7 @@
         </is>
       </c>
       <c r="E366" s="4" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="F366" s="3" t="inlineStr">
         <is>
@@ -23416,7 +23416,7 @@
         <v>16598000</v>
       </c>
       <c r="I366" s="5" t="n">
-        <v>21444</v>
+        <v>21528</v>
       </c>
       <c r="J366" s="3" t="inlineStr">
         <is>
@@ -23427,7 +23427,7 @@
         <v>16598000</v>
       </c>
       <c r="L366" s="5" t="n">
-        <v>21444</v>
+        <v>21528</v>
       </c>
       <c r="M366" s="3" t="inlineStr">
         <is>
@@ -24082,7 +24082,7 @@
         </is>
       </c>
       <c r="E377" s="4" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F377" s="3" t="inlineStr">
         <is>
@@ -24098,7 +24098,7 @@
         <v>9848000</v>
       </c>
       <c r="I377" s="5" t="n">
-        <v>19815</v>
+        <v>19775</v>
       </c>
       <c r="J377" s="3" t="inlineStr">
         <is>
@@ -24109,7 +24109,7 @@
         <v>9848000</v>
       </c>
       <c r="L377" s="5" t="n">
-        <v>19815</v>
+        <v>19775</v>
       </c>
       <c r="M377" s="3" t="inlineStr">
         <is>
@@ -24206,7 +24206,7 @@
         </is>
       </c>
       <c r="E379" s="4" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="F379" s="3" t="inlineStr">
         <is>
@@ -24222,7 +24222,7 @@
         <v>16808000</v>
       </c>
       <c r="I379" s="5" t="n">
-        <v>21716</v>
+        <v>21800</v>
       </c>
       <c r="J379" s="3" t="inlineStr">
         <is>
@@ -24233,7 +24233,7 @@
         <v>16808000</v>
       </c>
       <c r="L379" s="5" t="n">
-        <v>21716</v>
+        <v>21800</v>
       </c>
       <c r="M379" s="3" t="inlineStr">
         <is>
@@ -24888,7 +24888,7 @@
         </is>
       </c>
       <c r="E390" s="4" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F390" s="3" t="inlineStr">
         <is>
@@ -24904,7 +24904,7 @@
         <v>9778000</v>
       </c>
       <c r="I390" s="5" t="n">
-        <v>19674</v>
+        <v>19635</v>
       </c>
       <c r="J390" s="3" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
         <v>9778000</v>
       </c>
       <c r="L390" s="5" t="n">
-        <v>19674</v>
+        <v>19635</v>
       </c>
       <c r="M390" s="3" t="inlineStr">
         <is>
@@ -25012,7 +25012,7 @@
         </is>
       </c>
       <c r="E392" s="4" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="F392" s="3" t="inlineStr">
         <is>
@@ -25028,7 +25028,7 @@
         <v>16808000</v>
       </c>
       <c r="I392" s="5" t="n">
-        <v>21716</v>
+        <v>21800</v>
       </c>
       <c r="J392" s="3" t="inlineStr">
         <is>
@@ -25039,7 +25039,7 @@
         <v>16808000</v>
       </c>
       <c r="L392" s="5" t="n">
-        <v>21716</v>
+        <v>21800</v>
       </c>
       <c r="M392" s="3" t="inlineStr">
         <is>
@@ -25648,7 +25648,7 @@
         </is>
       </c>
       <c r="E402" s="4" t="n">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F402" s="3" t="inlineStr">
         <is>
@@ -25664,7 +25664,7 @@
         <v>14538000</v>
       </c>
       <c r="I402" s="5" t="n">
-        <v>27073</v>
+        <v>27022</v>
       </c>
       <c r="J402" s="3" t="inlineStr">
         <is>
@@ -25675,7 +25675,7 @@
         <v>14538000</v>
       </c>
       <c r="L402" s="5" t="n">
-        <v>27073</v>
+        <v>27022</v>
       </c>
       <c r="M402" s="3" t="inlineStr">
         <is>
@@ -26804,7 +26804,7 @@
         </is>
       </c>
       <c r="E420" s="4" t="n">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F420" s="3" t="inlineStr">
         <is>
@@ -26820,7 +26820,7 @@
         <v>11480000</v>
       </c>
       <c r="I420" s="5" t="n">
-        <v>21378</v>
+        <v>21338</v>
       </c>
       <c r="J420" s="3" t="inlineStr">
         <is>
@@ -26831,7 +26831,7 @@
         <v>11480000</v>
       </c>
       <c r="L420" s="5" t="n">
-        <v>21378</v>
+        <v>21338</v>
       </c>
       <c r="M420" s="3" t="inlineStr">
         <is>
@@ -26866,7 +26866,7 @@
         </is>
       </c>
       <c r="E421" s="4" t="n">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F421" s="3" t="inlineStr">
         <is>
@@ -26882,7 +26882,7 @@
         <v>8117000</v>
       </c>
       <c r="I421" s="5" t="n">
-        <v>18789</v>
+        <v>18833</v>
       </c>
       <c r="J421" s="3" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>8117000</v>
       </c>
       <c r="L421" s="5" t="n">
-        <v>18789</v>
+        <v>18833</v>
       </c>
       <c r="M421" s="3" t="inlineStr">
         <is>
@@ -27424,7 +27424,7 @@
         </is>
       </c>
       <c r="E430" s="4" t="n">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F430" s="3" t="inlineStr">
         <is>
@@ -27440,7 +27440,7 @@
         <v>8073000</v>
       </c>
       <c r="I430" s="5" t="n">
-        <v>18688</v>
+        <v>18731</v>
       </c>
       <c r="J430" s="3" t="inlineStr">
         <is>
@@ -27451,7 +27451,7 @@
         <v>8073000</v>
       </c>
       <c r="L430" s="5" t="n">
-        <v>18688</v>
+        <v>18731</v>
       </c>
       <c r="M430" s="3" t="inlineStr">
         <is>
@@ -27982,7 +27982,7 @@
         </is>
       </c>
       <c r="E439" s="4" t="n">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F439" s="3" t="inlineStr">
         <is>
@@ -27998,7 +27998,7 @@
         <v>8058000</v>
       </c>
       <c r="I439" s="5" t="n">
-        <v>18653</v>
+        <v>18696</v>
       </c>
       <c r="J439" s="3" t="inlineStr">
         <is>
@@ -28009,7 +28009,7 @@
         <v>8058000</v>
       </c>
       <c r="L439" s="5" t="n">
-        <v>18653</v>
+        <v>18696</v>
       </c>
       <c r="M439" s="3" t="inlineStr">
         <is>
@@ -28540,7 +28540,7 @@
         </is>
       </c>
       <c r="E448" s="4" t="n">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F448" s="3" t="inlineStr">
         <is>
@@ -28556,7 +28556,7 @@
         <v>8031000</v>
       </c>
       <c r="I448" s="5" t="n">
-        <v>18590</v>
+        <v>18633</v>
       </c>
       <c r="J448" s="3" t="inlineStr">
         <is>
@@ -28567,7 +28567,7 @@
         <v>8031000</v>
       </c>
       <c r="L448" s="5" t="n">
-        <v>18590</v>
+        <v>18633</v>
       </c>
       <c r="M448" s="3" t="inlineStr">
         <is>
@@ -29036,7 +29036,7 @@
         </is>
       </c>
       <c r="E456" s="4" t="n">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F456" s="3" t="inlineStr">
         <is>
@@ -29052,7 +29052,7 @@
         <v>10600000</v>
       </c>
       <c r="I456" s="5" t="n">
-        <v>19739</v>
+        <v>19703</v>
       </c>
       <c r="J456" s="3" t="inlineStr">
         <is>
@@ -29063,7 +29063,7 @@
         <v>10600000</v>
       </c>
       <c r="L456" s="5" t="n">
-        <v>19739</v>
+        <v>19703</v>
       </c>
       <c r="M456" s="3" t="inlineStr">
         <is>
@@ -29098,7 +29098,7 @@
         </is>
       </c>
       <c r="E457" s="4" t="n">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F457" s="3" t="inlineStr">
         <is>
@@ -29114,7 +29114,7 @@
         <v>7572000</v>
       </c>
       <c r="I457" s="5" t="n">
-        <v>17528</v>
+        <v>17568</v>
       </c>
       <c r="J457" s="3" t="inlineStr">
         <is>
@@ -29125,7 +29125,7 @@
         <v>7572000</v>
       </c>
       <c r="L457" s="5" t="n">
-        <v>17528</v>
+        <v>17568</v>
       </c>
       <c r="M457" s="3" t="inlineStr">
         <is>
@@ -32454,7 +32454,7 @@
         </is>
       </c>
       <c r="E511" s="4" t="n">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F511" s="3" t="inlineStr">
         <is>
@@ -32470,7 +32470,7 @@
         <v>7809000</v>
       </c>
       <c r="I511" s="5" t="n">
-        <v>18076</v>
+        <v>18118</v>
       </c>
       <c r="J511" s="3" t="inlineStr">
         <is>
@@ -32481,7 +32481,7 @@
         <v>7809000</v>
       </c>
       <c r="L511" s="5" t="n">
-        <v>18076</v>
+        <v>18118</v>
       </c>
       <c r="M511" s="3" t="inlineStr">
         <is>
@@ -32950,7 +32950,7 @@
         </is>
       </c>
       <c r="E519" s="4" t="n">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F519" s="3" t="inlineStr">
         <is>
@@ -32966,7 +32966,7 @@
         <v>10255000</v>
       </c>
       <c r="I519" s="5" t="n">
-        <v>19097</v>
+        <v>19061</v>
       </c>
       <c r="J519" s="3" t="inlineStr">
         <is>
@@ -32977,7 +32977,7 @@
         <v>10255000</v>
       </c>
       <c r="L519" s="5" t="n">
-        <v>19097</v>
+        <v>19061</v>
       </c>
       <c r="M519" s="3" t="inlineStr">
         <is>
@@ -33570,7 +33570,7 @@
         </is>
       </c>
       <c r="E529" s="4" t="n">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F529" s="3" t="inlineStr">
         <is>
@@ -33586,7 +33586,7 @@
         <v>7768000</v>
       </c>
       <c r="I529" s="5" t="n">
-        <v>17981</v>
+        <v>18023</v>
       </c>
       <c r="J529" s="3" t="inlineStr">
         <is>
@@ -33597,7 +33597,7 @@
         <v>7768000</v>
       </c>
       <c r="L529" s="5" t="n">
-        <v>17981</v>
+        <v>18023</v>
       </c>
       <c r="M529" s="3" t="inlineStr">
         <is>
@@ -35810,7 +35810,7 @@
         </is>
       </c>
       <c r="E565" s="4" t="n">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F565" s="3" t="inlineStr">
         <is>
@@ -35826,7 +35826,7 @@
         <v>7140000</v>
       </c>
       <c r="I565" s="5" t="n">
-        <v>16528</v>
+        <v>16566</v>
       </c>
       <c r="J565" s="3" t="inlineStr">
         <is>
@@ -35837,7 +35837,7 @@
         <v>7140000</v>
       </c>
       <c r="L565" s="5" t="n">
-        <v>16528</v>
+        <v>16566</v>
       </c>
       <c r="M565" s="3" t="inlineStr">
         <is>
@@ -37492,7 +37492,7 @@
         </is>
       </c>
       <c r="E592" s="4" t="n">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F592" s="3" t="inlineStr">
         <is>
@@ -37508,7 +37508,7 @@
         <v>7099000</v>
       </c>
       <c r="I592" s="5" t="n">
-        <v>16433</v>
+        <v>16471</v>
       </c>
       <c r="J592" s="3" t="inlineStr">
         <is>
@@ -37519,7 +37519,7 @@
         <v>7099000</v>
       </c>
       <c r="L592" s="5" t="n">
-        <v>16433</v>
+        <v>16471</v>
       </c>
       <c r="M592" s="3" t="inlineStr">
         <is>
@@ -37988,7 +37988,7 @@
         </is>
       </c>
       <c r="E600" s="4" t="n">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F600" s="3" t="inlineStr">
         <is>
@@ -38004,7 +38004,7 @@
         <v>9617000</v>
       </c>
       <c r="I600" s="5" t="n">
-        <v>17909</v>
+        <v>17875</v>
       </c>
       <c r="J600" s="3" t="inlineStr">
         <is>
@@ -38015,7 +38015,7 @@
         <v>9617000</v>
       </c>
       <c r="L600" s="5" t="n">
-        <v>17909</v>
+        <v>17875</v>
       </c>
       <c r="M600" s="3" t="inlineStr">
         <is>
@@ -38608,7 +38608,7 @@
         </is>
       </c>
       <c r="E610" s="4" t="n">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F610" s="3" t="inlineStr">
         <is>
@@ -38624,7 +38624,7 @@
         <v>7008000</v>
       </c>
       <c r="I610" s="5" t="n">
-        <v>16222</v>
+        <v>16260</v>
       </c>
       <c r="J610" s="3" t="inlineStr">
         <is>
@@ -38635,7 +38635,7 @@
         <v>7008000</v>
       </c>
       <c r="L610" s="5" t="n">
-        <v>16222</v>
+        <v>16260</v>
       </c>
       <c r="M610" s="3" t="inlineStr">
         <is>
@@ -39166,7 +39166,7 @@
         </is>
       </c>
       <c r="E619" s="4" t="n">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F619" s="3" t="inlineStr">
         <is>
@@ -39182,7 +39182,7 @@
         <v>6993000</v>
       </c>
       <c r="I619" s="5" t="n">
-        <v>16188</v>
+        <v>16225</v>
       </c>
       <c r="J619" s="3" t="inlineStr">
         <is>
@@ -39193,7 +39193,7 @@
         <v>6993000</v>
       </c>
       <c r="L619" s="5" t="n">
-        <v>16188</v>
+        <v>16225</v>
       </c>
       <c r="M619" s="3" t="inlineStr">
         <is>
@@ -40840,7 +40840,7 @@
         </is>
       </c>
       <c r="E646" s="4" t="n">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F646" s="3" t="inlineStr">
         <is>
@@ -40856,7 +40856,7 @@
         <v>7543000</v>
       </c>
       <c r="I646" s="5" t="n">
-        <v>17461</v>
+        <v>17501</v>
       </c>
       <c r="J646" s="3" t="inlineStr">
         <is>
@@ -40867,7 +40867,7 @@
         <v>7543000</v>
       </c>
       <c r="L646" s="5" t="n">
-        <v>17461</v>
+        <v>17501</v>
       </c>
       <c r="M646" s="3" t="inlineStr">
         <is>
@@ -46526,7 +46526,7 @@
         </is>
       </c>
       <c r="E735" s="4" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F735" s="3" t="inlineStr">
         <is>
@@ -46542,7 +46542,7 @@
         <v>6808000</v>
       </c>
       <c r="I735" s="5" t="n">
-        <v>22248</v>
+        <v>22321</v>
       </c>
       <c r="J735" s="3" t="inlineStr">
         <is>
@@ -46553,7 +46553,7 @@
         <v>6808000</v>
       </c>
       <c r="L735" s="5" t="n">
-        <v>22248</v>
+        <v>22321</v>
       </c>
       <c r="M735" s="3" t="inlineStr">
         <is>
@@ -46650,7 +46650,7 @@
         </is>
       </c>
       <c r="E737" s="4" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F737" s="3" t="inlineStr">
         <is>
@@ -46666,7 +46666,7 @@
         <v>9050000</v>
       </c>
       <c r="I737" s="5" t="n">
-        <v>29575</v>
+        <v>29672</v>
       </c>
       <c r="J737" s="3" t="inlineStr">
         <is>
@@ -46677,7 +46677,7 @@
         <v>6787500</v>
       </c>
       <c r="L737" s="5" t="n">
-        <v>22181</v>
+        <v>22254</v>
       </c>
       <c r="M737" s="3" t="inlineStr">
         <is>
@@ -47286,7 +47286,7 @@
         </is>
       </c>
       <c r="E747" s="4" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F747" s="3" t="inlineStr">
         <is>
@@ -47302,7 +47302,7 @@
         <v>6728000</v>
       </c>
       <c r="I747" s="5" t="n">
-        <v>21987</v>
+        <v>22059</v>
       </c>
       <c r="J747" s="3" t="inlineStr">
         <is>
@@ -47313,7 +47313,7 @@
         <v>6728000</v>
       </c>
       <c r="L747" s="5" t="n">
-        <v>21987</v>
+        <v>22059</v>
       </c>
       <c r="M747" s="3" t="inlineStr">
         <is>
@@ -47976,7 +47976,7 @@
         </is>
       </c>
       <c r="E758" s="4" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F758" s="3" t="inlineStr">
         <is>
@@ -47992,7 +47992,7 @@
         <v>9355000</v>
       </c>
       <c r="I758" s="5" t="n">
-        <v>21807</v>
+        <v>21756</v>
       </c>
       <c r="J758" s="3" t="inlineStr">
         <is>
@@ -48003,7 +48003,7 @@
         <v>9355000</v>
       </c>
       <c r="L758" s="5" t="n">
-        <v>21807</v>
+        <v>21756</v>
       </c>
       <c r="M758" s="3" t="inlineStr">
         <is>
@@ -48038,7 +48038,7 @@
         </is>
       </c>
       <c r="E759" s="4" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F759" s="3" t="inlineStr">
         <is>
@@ -48054,7 +48054,7 @@
         <v>6468000</v>
       </c>
       <c r="I759" s="5" t="n">
-        <v>21137</v>
+        <v>21207</v>
       </c>
       <c r="J759" s="3" t="inlineStr">
         <is>
@@ -48065,7 +48065,7 @@
         <v>6468000</v>
       </c>
       <c r="L759" s="5" t="n">
-        <v>21137</v>
+        <v>21207</v>
       </c>
       <c r="M759" s="3" t="inlineStr">
         <is>
@@ -48162,7 +48162,7 @@
         </is>
       </c>
       <c r="E761" s="4" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F761" s="3" t="inlineStr">
         <is>
@@ -48178,7 +48178,7 @@
         <v>6456000</v>
       </c>
       <c r="I761" s="5" t="n">
-        <v>21098</v>
+        <v>21167</v>
       </c>
       <c r="J761" s="3" t="inlineStr">
         <is>
@@ -48189,7 +48189,7 @@
         <v>6456000</v>
       </c>
       <c r="L761" s="5" t="n">
-        <v>21098</v>
+        <v>21167</v>
       </c>
       <c r="M761" s="3" t="inlineStr">
         <is>
@@ -48728,7 +48728,7 @@
         </is>
       </c>
       <c r="E770" s="4" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F770" s="3" t="inlineStr">
         <is>
@@ -48744,7 +48744,7 @@
         <v>9248000</v>
       </c>
       <c r="I770" s="5" t="n">
-        <v>21557</v>
+        <v>21507</v>
       </c>
       <c r="J770" s="3" t="inlineStr">
         <is>
@@ -48755,7 +48755,7 @@
         <v>9248000</v>
       </c>
       <c r="L770" s="5" t="n">
-        <v>21557</v>
+        <v>21507</v>
       </c>
       <c r="M770" s="3" t="inlineStr">
         <is>
@@ -48790,7 +48790,7 @@
         </is>
       </c>
       <c r="E771" s="4" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F771" s="3" t="inlineStr">
         <is>
@@ -48806,7 +48806,7 @@
         <v>6388000</v>
       </c>
       <c r="I771" s="5" t="n">
-        <v>20876</v>
+        <v>20944</v>
       </c>
       <c r="J771" s="3" t="inlineStr">
         <is>
@@ -48817,7 +48817,7 @@
         <v>6388000</v>
       </c>
       <c r="L771" s="5" t="n">
-        <v>20876</v>
+        <v>20944</v>
       </c>
       <c r="M771" s="3" t="inlineStr">
         <is>
@@ -48914,7 +48914,7 @@
         </is>
       </c>
       <c r="E773" s="4" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F773" s="3" t="inlineStr">
         <is>
@@ -48930,7 +48930,7 @@
         <v>5680000</v>
       </c>
       <c r="I773" s="5" t="n">
-        <v>18562</v>
+        <v>18623</v>
       </c>
       <c r="J773" s="3" t="inlineStr">
         <is>
@@ -48941,7 +48941,7 @@
         <v>5680000</v>
       </c>
       <c r="L773" s="5" t="n">
-        <v>18562</v>
+        <v>18623</v>
       </c>
       <c r="M773" s="3" t="inlineStr">
         <is>
@@ -49480,7 +49480,7 @@
         </is>
       </c>
       <c r="E782" s="4" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F782" s="3" t="inlineStr">
         <is>
@@ -49496,7 +49496,7 @@
         <v>9088000</v>
       </c>
       <c r="I782" s="5" t="n">
-        <v>21184</v>
+        <v>21135</v>
       </c>
       <c r="J782" s="3" t="inlineStr">
         <is>
@@ -49507,7 +49507,7 @@
         <v>9088000</v>
       </c>
       <c r="L782" s="5" t="n">
-        <v>21184</v>
+        <v>21135</v>
       </c>
       <c r="M782" s="3" t="inlineStr">
         <is>
@@ -49542,7 +49542,7 @@
         </is>
       </c>
       <c r="E783" s="4" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F783" s="3" t="inlineStr">
         <is>
@@ -49558,7 +49558,7 @@
         <v>6288000</v>
       </c>
       <c r="I783" s="5" t="n">
-        <v>20549</v>
+        <v>20616</v>
       </c>
       <c r="J783" s="3" t="inlineStr">
         <is>
@@ -49569,7 +49569,7 @@
         <v>6288000</v>
       </c>
       <c r="L783" s="5" t="n">
-        <v>20549</v>
+        <v>20616</v>
       </c>
       <c r="M783" s="3" t="inlineStr">
         <is>
@@ -49666,7 +49666,7 @@
         </is>
       </c>
       <c r="E785" s="4" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F785" s="3" t="inlineStr">
         <is>
@@ -49682,7 +49682,7 @@
         <v>5667000</v>
       </c>
       <c r="I785" s="5" t="n">
-        <v>18520</v>
+        <v>18580</v>
       </c>
       <c r="J785" s="3" t="inlineStr">
         <is>
@@ -49693,7 +49693,7 @@
         <v>5667000</v>
       </c>
       <c r="L785" s="5" t="n">
-        <v>18520</v>
+        <v>18580</v>
       </c>
       <c r="M785" s="3" t="inlineStr">
         <is>
@@ -50224,7 +50224,7 @@
         </is>
       </c>
       <c r="E794" s="4" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F794" s="3" t="inlineStr">
         <is>
@@ -50240,7 +50240,7 @@
         <v>8818000</v>
       </c>
       <c r="I794" s="5" t="n">
-        <v>20555</v>
+        <v>20507</v>
       </c>
       <c r="J794" s="3" t="inlineStr">
         <is>
@@ -50251,7 +50251,7 @@
         <v>8818000</v>
       </c>
       <c r="L794" s="5" t="n">
-        <v>20555</v>
+        <v>20507</v>
       </c>
       <c r="M794" s="3" t="inlineStr">
         <is>
@@ -50286,7 +50286,7 @@
         </is>
       </c>
       <c r="E795" s="4" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F795" s="3" t="inlineStr">
         <is>
@@ -50302,7 +50302,7 @@
         <v>6025000</v>
       </c>
       <c r="I795" s="5" t="n">
-        <v>19690</v>
+        <v>19754</v>
       </c>
       <c r="J795" s="3" t="inlineStr">
         <is>
@@ -50313,7 +50313,7 @@
         <v>6025000</v>
       </c>
       <c r="L795" s="5" t="n">
-        <v>19690</v>
+        <v>19754</v>
       </c>
       <c r="M795" s="3" t="inlineStr">
         <is>
@@ -50410,7 +50410,7 @@
         </is>
       </c>
       <c r="E797" s="4" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F797" s="3" t="inlineStr">
         <is>
@@ -50426,7 +50426,7 @@
         <v>5655000</v>
       </c>
       <c r="I797" s="5" t="n">
-        <v>18480</v>
+        <v>18541</v>
       </c>
       <c r="J797" s="3" t="inlineStr">
         <is>
@@ -50437,7 +50437,7 @@
         <v>5655000</v>
       </c>
       <c r="L797" s="5" t="n">
-        <v>18480</v>
+        <v>18541</v>
       </c>
       <c r="M797" s="3" t="inlineStr">
         <is>
@@ -50968,7 +50968,7 @@
         </is>
       </c>
       <c r="E806" s="4" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F806" s="3" t="inlineStr">
         <is>
@@ -50984,7 +50984,7 @@
         <v>8628000</v>
       </c>
       <c r="I806" s="5" t="n">
-        <v>20112</v>
+        <v>20065</v>
       </c>
       <c r="J806" s="3" t="inlineStr">
         <is>
@@ -50995,7 +50995,7 @@
         <v>8628000</v>
       </c>
       <c r="L806" s="5" t="n">
-        <v>20112</v>
+        <v>20065</v>
       </c>
       <c r="M806" s="3" t="inlineStr">
         <is>
@@ -51030,7 +51030,7 @@
         </is>
       </c>
       <c r="E807" s="4" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F807" s="3" t="inlineStr">
         <is>
@@ -51046,7 +51046,7 @@
         <v>6108000</v>
       </c>
       <c r="I807" s="5" t="n">
-        <v>19961</v>
+        <v>20026</v>
       </c>
       <c r="J807" s="3" t="inlineStr">
         <is>
@@ -51057,7 +51057,7 @@
         <v>6108000</v>
       </c>
       <c r="L807" s="5" t="n">
-        <v>19961</v>
+        <v>20026</v>
       </c>
       <c r="M807" s="3" t="inlineStr">
         <is>
@@ -51712,7 +51712,7 @@
         </is>
       </c>
       <c r="E818" s="4" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F818" s="3" t="inlineStr">
         <is>
@@ -51728,7 +51728,7 @@
         <v>8370000</v>
       </c>
       <c r="I818" s="5" t="n">
-        <v>19510</v>
+        <v>19465</v>
       </c>
       <c r="J818" s="3" t="inlineStr">
         <is>
@@ -51739,7 +51739,7 @@
         <v>8370000</v>
       </c>
       <c r="L818" s="5" t="n">
-        <v>19510</v>
+        <v>19465</v>
       </c>
       <c r="M818" s="3" t="inlineStr">
         <is>
@@ -51774,7 +51774,7 @@
         </is>
       </c>
       <c r="E819" s="4" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F819" s="3" t="inlineStr">
         <is>
@@ -51790,7 +51790,7 @@
         <v>5980000</v>
       </c>
       <c r="I819" s="5" t="n">
-        <v>19542</v>
+        <v>19607</v>
       </c>
       <c r="J819" s="3" t="inlineStr">
         <is>
@@ -51801,7 +51801,7 @@
         <v>5980000</v>
       </c>
       <c r="L819" s="5" t="n">
-        <v>19542</v>
+        <v>19607</v>
       </c>
       <c r="M819" s="3" t="inlineStr">
         <is>
@@ -52456,7 +52456,7 @@
         </is>
       </c>
       <c r="E830" s="4" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F830" s="3" t="inlineStr">
         <is>
@@ -52472,7 +52472,7 @@
         <v>8468000</v>
       </c>
       <c r="I830" s="5" t="n">
-        <v>19739</v>
+        <v>19693</v>
       </c>
       <c r="J830" s="3" t="inlineStr">
         <is>
@@ -52483,7 +52483,7 @@
         <v>8468000</v>
       </c>
       <c r="L830" s="5" t="n">
-        <v>19739</v>
+        <v>19693</v>
       </c>
       <c r="M830" s="3" t="inlineStr">
         <is>
@@ -52518,7 +52518,7 @@
         </is>
       </c>
       <c r="E831" s="4" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F831" s="3" t="inlineStr">
         <is>
@@ -52534,7 +52534,7 @@
         <v>6068000</v>
       </c>
       <c r="I831" s="5" t="n">
-        <v>19830</v>
+        <v>19895</v>
       </c>
       <c r="J831" s="3" t="inlineStr">
         <is>
@@ -52545,7 +52545,7 @@
         <v>6068000</v>
       </c>
       <c r="L831" s="5" t="n">
-        <v>19830</v>
+        <v>19895</v>
       </c>
       <c r="M831" s="3" t="inlineStr">
         <is>
@@ -53262,7 +53262,7 @@
         </is>
       </c>
       <c r="E843" s="4" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F843" s="3" t="inlineStr">
         <is>
@@ -53278,7 +53278,7 @@
         <v>5718000</v>
       </c>
       <c r="I843" s="5" t="n">
-        <v>18686</v>
+        <v>18748</v>
       </c>
       <c r="J843" s="3" t="inlineStr">
         <is>
@@ -53289,7 +53289,7 @@
         <v>5718000</v>
       </c>
       <c r="L843" s="5" t="n">
-        <v>18686</v>
+        <v>18748</v>
       </c>
       <c r="M843" s="3" t="inlineStr">
         <is>
@@ -53944,7 +53944,7 @@
         </is>
       </c>
       <c r="E854" s="4" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F854" s="3" t="inlineStr">
         <is>
@@ -53960,7 +53960,7 @@
         <v>8142000</v>
       </c>
       <c r="I854" s="5" t="n">
-        <v>18979</v>
+        <v>18935</v>
       </c>
       <c r="J854" s="3" t="inlineStr">
         <is>
@@ -53971,7 +53971,7 @@
         <v>8142000</v>
       </c>
       <c r="L854" s="5" t="n">
-        <v>18979</v>
+        <v>18935</v>
       </c>
       <c r="M854" s="3" t="inlineStr">
         <is>
@@ -54006,7 +54006,7 @@
         </is>
       </c>
       <c r="E855" s="4" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F855" s="3" t="inlineStr">
         <is>
@@ -54022,7 +54022,7 @@
         <v>5698000</v>
       </c>
       <c r="I855" s="5" t="n">
-        <v>18621</v>
+        <v>18682</v>
       </c>
       <c r="J855" s="3" t="inlineStr">
         <is>
@@ -54033,7 +54033,7 @@
         <v>5698000</v>
       </c>
       <c r="L855" s="5" t="n">
-        <v>18621</v>
+        <v>18682</v>
       </c>
       <c r="M855" s="3" t="inlineStr">
         <is>
@@ -55432,7 +55432,7 @@
         </is>
       </c>
       <c r="E878" s="4" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F878" s="3" t="inlineStr">
         <is>
@@ -55448,7 +55448,7 @@
         <v>8093000</v>
       </c>
       <c r="I878" s="5" t="n">
-        <v>18865</v>
+        <v>18821</v>
       </c>
       <c r="J878" s="3" t="inlineStr">
         <is>
@@ -55459,7 +55459,7 @@
         <v>8093000</v>
       </c>
       <c r="L878" s="5" t="n">
-        <v>18865</v>
+        <v>18821</v>
       </c>
       <c r="M878" s="3" t="inlineStr">
         <is>
@@ -55494,7 +55494,7 @@
         </is>
       </c>
       <c r="E879" s="4" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F879" s="3" t="inlineStr">
         <is>
@@ -55510,7 +55510,7 @@
         <v>5658000</v>
       </c>
       <c r="I879" s="5" t="n">
-        <v>18490</v>
+        <v>18551</v>
       </c>
       <c r="J879" s="3" t="inlineStr">
         <is>
@@ -55521,7 +55521,7 @@
         <v>5658000</v>
       </c>
       <c r="L879" s="5" t="n">
-        <v>18490</v>
+        <v>18551</v>
       </c>
       <c r="M879" s="3" t="inlineStr">
         <is>
@@ -56238,7 +56238,7 @@
         </is>
       </c>
       <c r="E891" s="4" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F891" s="3" t="inlineStr">
         <is>
@@ -56254,7 +56254,7 @@
         <v>5638000</v>
       </c>
       <c r="I891" s="5" t="n">
-        <v>18425</v>
+        <v>18485</v>
       </c>
       <c r="J891" s="3" t="inlineStr">
         <is>
@@ -56265,7 +56265,7 @@
         <v>5638000</v>
       </c>
       <c r="L891" s="5" t="n">
-        <v>18425</v>
+        <v>18485</v>
       </c>
       <c r="M891" s="3" t="inlineStr">
         <is>
@@ -56362,7 +56362,7 @@
         </is>
       </c>
       <c r="E893" s="4" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F893" s="3" t="inlineStr">
         <is>
@@ -56378,7 +56378,7 @@
         <v>5528000</v>
       </c>
       <c r="I893" s="5" t="n">
-        <v>18065</v>
+        <v>18125</v>
       </c>
       <c r="J893" s="3" t="inlineStr">
         <is>
@@ -56389,7 +56389,7 @@
         <v>5528000</v>
       </c>
       <c r="L893" s="5" t="n">
-        <v>18065</v>
+        <v>18125</v>
       </c>
       <c r="M893" s="3" t="inlineStr">
         <is>
@@ -56920,7 +56920,7 @@
         </is>
       </c>
       <c r="E902" s="4" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F902" s="3" t="inlineStr">
         <is>
@@ -56936,7 +56936,7 @@
         <v>8043000</v>
       </c>
       <c r="I902" s="5" t="n">
-        <v>18748</v>
+        <v>18705</v>
       </c>
       <c r="J902" s="3" t="inlineStr">
         <is>
@@ -56947,7 +56947,7 @@
         <v>8043000</v>
       </c>
       <c r="L902" s="5" t="n">
-        <v>18748</v>
+        <v>18705</v>
       </c>
       <c r="M902" s="3" t="inlineStr">
         <is>
@@ -56982,7 +56982,7 @@
         </is>
       </c>
       <c r="E903" s="4" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F903" s="3" t="inlineStr">
         <is>
@@ -56998,7 +56998,7 @@
         <v>5618000</v>
       </c>
       <c r="I903" s="5" t="n">
-        <v>18359</v>
+        <v>18420</v>
       </c>
       <c r="J903" s="3" t="inlineStr">
         <is>
@@ -57009,7 +57009,7 @@
         <v>5618000</v>
       </c>
       <c r="L903" s="5" t="n">
-        <v>18359</v>
+        <v>18420</v>
       </c>
       <c r="M903" s="3" t="inlineStr">
         <is>
@@ -57726,7 +57726,7 @@
         </is>
       </c>
       <c r="E915" s="4" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F915" s="3" t="inlineStr">
         <is>
@@ -57742,7 +57742,7 @@
         <v>5600000</v>
       </c>
       <c r="I915" s="5" t="n">
-        <v>18301</v>
+        <v>18361</v>
       </c>
       <c r="J915" s="3" t="inlineStr">
         <is>
@@ -57753,7 +57753,7 @@
         <v>5600000</v>
       </c>
       <c r="L915" s="5" t="n">
-        <v>18301</v>
+        <v>18361</v>
       </c>
       <c r="M915" s="3" t="inlineStr">
         <is>
@@ -58470,7 +58470,7 @@
         </is>
       </c>
       <c r="E927" s="4" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F927" s="3" t="inlineStr">
         <is>
@@ -58486,7 +58486,7 @@
         <v>5590000</v>
       </c>
       <c r="I927" s="5" t="n">
-        <v>18268</v>
+        <v>18328</v>
       </c>
       <c r="J927" s="3" t="inlineStr">
         <is>
@@ -58497,7 +58497,7 @@
         <v>5590000</v>
       </c>
       <c r="L927" s="5" t="n">
-        <v>18268</v>
+        <v>18328</v>
       </c>
       <c r="M927" s="3" t="inlineStr">
         <is>
@@ -59214,7 +59214,7 @@
         </is>
       </c>
       <c r="E939" s="4" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F939" s="3" t="inlineStr">
         <is>
@@ -59230,7 +59230,7 @@
         <v>5488000</v>
       </c>
       <c r="I939" s="5" t="n">
-        <v>17935</v>
+        <v>17993</v>
       </c>
       <c r="J939" s="3" t="inlineStr">
         <is>
@@ -59241,7 +59241,7 @@
         <v>5488000</v>
       </c>
       <c r="L939" s="5" t="n">
-        <v>17935</v>
+        <v>17993</v>
       </c>
       <c r="M939" s="3" t="inlineStr">
         <is>
@@ -59958,7 +59958,7 @@
         </is>
       </c>
       <c r="E951" s="4" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F951" s="3" t="inlineStr">
         <is>
@@ -59974,7 +59974,7 @@
         <v>5456000</v>
       </c>
       <c r="I951" s="5" t="n">
-        <v>17830</v>
+        <v>17889</v>
       </c>
       <c r="J951" s="3" t="inlineStr">
         <is>
@@ -59985,7 +59985,7 @@
         <v>5456000</v>
       </c>
       <c r="L951" s="5" t="n">
-        <v>17830</v>
+        <v>17889</v>
       </c>
       <c r="M951" s="3" t="inlineStr">
         <is>
@@ -60082,7 +60082,7 @@
         </is>
       </c>
       <c r="E953" s="4" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F953" s="3" t="inlineStr">
         <is>
@@ -60098,7 +60098,7 @@
         <v>5419000</v>
       </c>
       <c r="I953" s="5" t="n">
-        <v>17709</v>
+        <v>17767</v>
       </c>
       <c r="J953" s="3" t="inlineStr">
         <is>
@@ -60109,7 +60109,7 @@
         <v>5419000</v>
       </c>
       <c r="L953" s="5" t="n">
-        <v>17709</v>
+        <v>17767</v>
       </c>
       <c r="M953" s="3" t="inlineStr">
         <is>
@@ -60826,7 +60826,7 @@
         </is>
       </c>
       <c r="E965" s="4" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F965" s="3" t="inlineStr">
         <is>
@@ -60842,7 +60842,7 @@
         <v>5405000</v>
       </c>
       <c r="I965" s="5" t="n">
-        <v>17663</v>
+        <v>17721</v>
       </c>
       <c r="J965" s="3" t="inlineStr">
         <is>
@@ -60853,7 +60853,7 @@
         <v>5405000</v>
       </c>
       <c r="L965" s="5" t="n">
-        <v>17663</v>
+        <v>17721</v>
       </c>
       <c r="M965" s="3" t="inlineStr">
         <is>
@@ -61446,7 +61446,7 @@
         </is>
       </c>
       <c r="E975" s="4" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F975" s="3" t="inlineStr">
         <is>
@@ -61462,7 +61462,7 @@
         <v>5338000</v>
       </c>
       <c r="I975" s="5" t="n">
-        <v>17444</v>
+        <v>17502</v>
       </c>
       <c r="J975" s="3" t="inlineStr">
         <is>
@@ -61473,7 +61473,7 @@
         <v>5338000</v>
       </c>
       <c r="L975" s="5" t="n">
-        <v>17444</v>
+        <v>17502</v>
       </c>
       <c r="M975" s="3" t="inlineStr">
         <is>
@@ -62190,7 +62190,7 @@
         </is>
       </c>
       <c r="E987" s="4" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F987" s="3" t="inlineStr">
         <is>
@@ -62206,7 +62206,7 @@
         <v>5260000</v>
       </c>
       <c r="I987" s="5" t="n">
-        <v>17190</v>
+        <v>17246</v>
       </c>
       <c r="J987" s="3" t="inlineStr">
         <is>
@@ -62217,7 +62217,7 @@
         <v>5260000</v>
       </c>
       <c r="L987" s="5" t="n">
-        <v>17190</v>
+        <v>17246</v>
       </c>
       <c r="M987" s="3" t="inlineStr">
         <is>
@@ -62314,7 +62314,7 @@
         </is>
       </c>
       <c r="E989" s="4" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F989" s="3" t="inlineStr">
         <is>
@@ -62330,7 +62330,7 @@
         <v>5250000</v>
       </c>
       <c r="I989" s="5" t="n">
-        <v>17157</v>
+        <v>17213</v>
       </c>
       <c r="J989" s="3" t="inlineStr">
         <is>
@@ -62341,7 +62341,7 @@
         <v>5250000</v>
       </c>
       <c r="L989" s="5" t="n">
-        <v>17157</v>
+        <v>17213</v>
       </c>
       <c r="M989" s="3" t="inlineStr">
         <is>
@@ -63058,7 +63058,7 @@
         </is>
       </c>
       <c r="E1001" s="4" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F1001" s="3" t="inlineStr">
         <is>
@@ -63074,7 +63074,7 @@
         <v>5188000</v>
       </c>
       <c r="I1001" s="5" t="n">
-        <v>16954</v>
+        <v>17010</v>
       </c>
       <c r="J1001" s="3" t="inlineStr">
         <is>
@@ -63085,7 +63085,7 @@
         <v>5188000</v>
       </c>
       <c r="L1001" s="5" t="n">
-        <v>16954</v>
+        <v>17010</v>
       </c>
       <c r="M1001" s="3" t="inlineStr">
         <is>
@@ -63616,7 +63616,7 @@
         </is>
       </c>
       <c r="E1010" s="4" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F1010" s="3" t="inlineStr">
         <is>
@@ -63632,7 +63632,7 @@
         <v>7100000</v>
       </c>
       <c r="I1010" s="5" t="n">
-        <v>16550</v>
+        <v>16512</v>
       </c>
       <c r="J1010" s="3" t="inlineStr">
         <is>
@@ -63643,7 +63643,7 @@
         <v>7100000</v>
       </c>
       <c r="L1010" s="5" t="n">
-        <v>16550</v>
+        <v>16512</v>
       </c>
       <c r="M1010" s="3" t="inlineStr">
         <is>
@@ -63678,7 +63678,7 @@
         </is>
       </c>
       <c r="E1011" s="4" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F1011" s="3" t="inlineStr">
         <is>
@@ -63694,7 +63694,7 @@
         <v>5188000</v>
       </c>
       <c r="I1011" s="5" t="n">
-        <v>16954</v>
+        <v>17010</v>
       </c>
       <c r="J1011" s="3" t="inlineStr">
         <is>
@@ -63705,7 +63705,7 @@
         <v>5188000</v>
       </c>
       <c r="L1011" s="5" t="n">
-        <v>16954</v>
+        <v>17010</v>
       </c>
       <c r="M1011" s="3" t="inlineStr">
         <is>
@@ -63802,7 +63802,7 @@
         </is>
       </c>
       <c r="E1013" s="4" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F1013" s="3" t="inlineStr">
         <is>
@@ -63818,7 +63818,7 @@
         <v>5188000</v>
       </c>
       <c r="I1013" s="5" t="n">
-        <v>16954</v>
+        <v>17010</v>
       </c>
       <c r="J1013" s="3" t="inlineStr">
         <is>
@@ -63829,7 +63829,7 @@
         <v>5188000</v>
       </c>
       <c r="L1013" s="5" t="n">
-        <v>16954</v>
+        <v>17010</v>
       </c>
       <c r="M1013" s="3" t="inlineStr">
         <is>
@@ -64058,7 +64058,7 @@
         </is>
       </c>
       <c r="E1017" s="4" t="n">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F1017" s="3" t="inlineStr">
         <is>
@@ -64074,7 +64074,7 @@
         <v>13128000</v>
       </c>
       <c r="I1017" s="5" t="n">
-        <v>25591</v>
+        <v>25541</v>
       </c>
       <c r="J1017" s="3" t="inlineStr">
         <is>
@@ -64085,7 +64085,7 @@
         <v>13128000</v>
       </c>
       <c r="L1017" s="5" t="n">
-        <v>25591</v>
+        <v>25541</v>
       </c>
       <c r="M1017" s="3" t="inlineStr">
         <is>
@@ -64120,7 +64120,7 @@
         </is>
       </c>
       <c r="E1018" s="4" t="n">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F1018" s="3" t="inlineStr">
         <is>
@@ -64136,7 +64136,7 @@
         <v>10656000</v>
       </c>
       <c r="I1018" s="5" t="n">
-        <v>23946</v>
+        <v>24000</v>
       </c>
       <c r="J1018" s="3" t="inlineStr">
         <is>
@@ -64147,7 +64147,7 @@
         <v>10656000</v>
       </c>
       <c r="L1018" s="5" t="n">
-        <v>23946</v>
+        <v>24000</v>
       </c>
       <c r="M1018" s="3" t="inlineStr">
         <is>
@@ -64637,9 +64637,9 @@
       </c>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t>A | 774呎 (3房)
+          <t>A | 771呎 (3房)
 $2144万
-$27,698/呎
+$27,805/呎
 (26年-06月-30日)</t>
         </is>
       </c>
@@ -64804,25 +64804,25 @@
       </c>
       <c r="I8" s="21" t="inlineStr">
         <is>
-          <t>H | 306呎 (1房)
+          <t>H | 305呎 (1房)
 $635万
-$20,745/呎
+$20,813/呎
 (26年-04月-02日)</t>
         </is>
       </c>
       <c r="J8" s="21" t="inlineStr">
         <is>
-          <t>J | 306呎 (1房)
+          <t>J | 305呎 (1房)
 $729万
-$23,817/呎
+$23,895/呎
 (26年-09月-15日)</t>
         </is>
       </c>
       <c r="K8" s="21" t="inlineStr">
         <is>
-          <t>K | 309呎 (1房)
+          <t>K | 308呎 (1房)
 $653万
-$21,126/呎
+$21,195/呎
 (26年-03月-30日)</t>
         </is>
       </c>
@@ -64859,9 +64859,9 @@
       </c>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t>A | 774呎 (3房)
+          <t>A | 771呎 (3房)
 $2007万
-$25,928/呎
+$26,029/呎
 (26年-06月-09日)</t>
         </is>
       </c>
@@ -64915,25 +64915,25 @@
       </c>
       <c r="I9" s="21" t="inlineStr">
         <is>
-          <t>H | 306呎 (1房)
+          <t>H | 305呎 (1房)
 $632万
-$20,647/呎
+$20,715/呎
 (26年-03月-27日)</t>
         </is>
       </c>
       <c r="J9" s="21" t="inlineStr">
         <is>
-          <t>J | 306呎 (1房)
+          <t>J | 305呎 (1房)
 $722万
-$23,588/呎
+$23,666/呎
 (26年-08月-11日)</t>
         </is>
       </c>
       <c r="K9" s="21" t="inlineStr">
         <is>
-          <t>K | 309呎 (1房)
+          <t>K | 308呎 (1房)
 $646万
-$20,890/呎
+$20,958/呎
 (26年-04月-08日)</t>
         </is>
       </c>
@@ -65034,17 +65034,17 @@
       </c>
       <c r="J10" s="21" t="inlineStr">
         <is>
-          <t>J | 306呎 (1房)
+          <t>J | 305呎 (1房)
 $696万
-$22,732/呎
+$22,807/呎
 (26年-07月-06日)</t>
         </is>
       </c>
       <c r="K10" s="21" t="inlineStr">
         <is>
-          <t>K | 309呎 (1房)
+          <t>K | 308呎 (1房)
 $615万
-$19,916/呎
+$19,981/呎
 (26年-03月-03日)</t>
         </is>
       </c>
@@ -65066,9 +65066,9 @@
       </c>
       <c r="N10" s="21" t="inlineStr">
         <is>
-          <t>N | 285呎 (1房)
+          <t>N | 288呎 (1房)
 $672万
-$23,579/呎
+$23,333/呎
 (26年-06月-10日)</t>
         </is>
       </c>
@@ -65081,9 +65081,9 @@
       </c>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t>A | 774呎 (3房)
+          <t>A | 771呎 (3房)
 $1889万
-$24,403/呎
+$24,498/呎
 (26年-02月-25日)</t>
         </is>
       </c>
@@ -65137,33 +65137,33 @@
       </c>
       <c r="I11" s="21" t="inlineStr">
         <is>
-          <t>H | 306呎 (1房)
+          <t>H | 305呎 (1房)
 $627万
-$20,484/呎
+$20,551/呎
 (26年-03月-24日)</t>
         </is>
       </c>
       <c r="J11" s="21" t="inlineStr">
         <is>
-          <t>J | 306呎 (1房)
+          <t>J | 305呎 (1房)
 $689万
-$22,516/呎
+$22,590/呎
 (26年-06月-25日)</t>
         </is>
       </c>
       <c r="K11" s="21" t="inlineStr">
         <is>
-          <t>K | 309呎 (1房)
+          <t>K | 308呎 (1房)
 $613万
-$19,848/呎
+$19,912/呎
 (26年-02月-12日)</t>
         </is>
       </c>
       <c r="L11" s="21" t="inlineStr">
         <is>
-          <t>L | 429呎 (2房)
+          <t>L | 430呎 (2房)
 $890万
-$20,744/呎
+$20,695/呎
 (24年-06月-24日)</t>
         </is>
       </c>
@@ -65177,9 +65177,9 @@
       </c>
       <c r="N11" s="21" t="inlineStr">
         <is>
-          <t>N | 285呎 (1房)
+          <t>N | 288呎 (1房)
 $679万
-$23,818/呎
+$23,569/呎
 (26年-07月-13日)</t>
         </is>
       </c>
@@ -65248,9 +65248,9 @@
       </c>
       <c r="I12" s="21" t="inlineStr">
         <is>
-          <t>H | 306呎 (1房)
+          <t>H | 305呎 (1房)
 $620万
-$20,261/呎
+$20,328/呎
 (26年-03月-19日)</t>
         </is>
       </c>
@@ -65288,9 +65288,9 @@
       </c>
       <c r="N12" s="21" t="inlineStr">
         <is>
-          <t>N | 285呎 (1房)
+          <t>N | 288呎 (1房)
 $672万
-$23,579/呎
+$23,333/呎
 (26年-06月-30日)</t>
         </is>
       </c>
@@ -65359,9 +65359,9 @@
       </c>
       <c r="I13" s="21" t="inlineStr">
         <is>
-          <t>H | 306呎 (1房)
+          <t>H | 305呎 (1房)
 $596万
-$19,471/呎
+$19,534/呎
 (26年-02月-24日)</t>
         </is>
       </c>
@@ -65399,9 +65399,9 @@
       </c>
       <c r="N13" s="21" t="inlineStr">
         <is>
-          <t>N | 285呎 (1房)
+          <t>N | 288呎 (1房)
 $631万
-$22,133/呎
+$21,903/呎
 (26年-04月-01日)</t>
         </is>
       </c>
@@ -65414,9 +65414,9 @@
       </c>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t>A | 774呎 (3房)
+          <t>A | 771呎 (3房)
 $1807万
-$23,344/呎
+$23,435/呎
 (26年-02月-16日)</t>
         </is>
       </c>
@@ -65470,9 +65470,9 @@
       </c>
       <c r="I14" s="21" t="inlineStr">
         <is>
-          <t>H | 306呎 (1房)
+          <t>H | 305呎 (1房)
 $592万
-$19,350/呎
+$19,413/呎
 (26年-02月-27日)</t>
         </is>
       </c>
@@ -65525,9 +65525,9 @@
       </c>
       <c r="B15" s="21" t="inlineStr">
         <is>
-          <t>A | 774呎 (3房)
+          <t>A | 771呎 (3房)
 $1755万
-$22,679/呎
+$22,768/呎
 (25年-07月-23日)</t>
         </is>
       </c>
@@ -65597,9 +65597,9 @@
       </c>
       <c r="K15" s="21" t="inlineStr">
         <is>
-          <t>K | 309呎 (1房)
+          <t>K | 308呎 (1房)
 $599万
-$19,382/呎
+$19,445/呎
 (25年-11月-05日)</t>
         </is>
       </c>
@@ -65636,9 +65636,9 @@
       </c>
       <c r="B16" s="21" t="inlineStr">
         <is>
-          <t>A | 774呎 (3房)
+          <t>A | 771呎 (3房)
 $1967万
-$25,411/呎
+$25,510/呎
 (26年-06月-02日)</t>
         </is>
       </c>
@@ -65732,9 +65732,9 @@
       </c>
       <c r="N16" s="21" t="inlineStr">
         <is>
-          <t>N | 285呎 (1房)
+          <t>N | 288呎 (1房)
 $598万
-$20,989/呎
+$20,771/呎
 (26年-01月-15日)</t>
         </is>
       </c>
@@ -65747,9 +65747,9 @@
       </c>
       <c r="B17" s="21" t="inlineStr">
         <is>
-          <t>A | 774呎 (3房)
+          <t>A | 771呎 (3房)
 $1774万
-$22,917/呎
+$23,006/呎
 (26年-03月-02日)</t>
         </is>
       </c>
@@ -65819,9 +65819,9 @@
       </c>
       <c r="K17" s="21" t="inlineStr">
         <is>
-          <t>K | 309呎 (1房)
+          <t>K | 308呎 (1房)
 $592万
-$19,162/呎
+$19,224/呎
 (25年-09月-22日)</t>
         </is>
       </c>
@@ -65843,9 +65843,9 @@
       </c>
       <c r="N17" s="21" t="inlineStr">
         <is>
-          <t>N | 285呎 (1房)
+          <t>N | 288呎 (1房)
 $594万
-$20,853/呎
+$20,635/呎
 (26年-01月-14日)</t>
         </is>
       </c>
@@ -65922,9 +65922,9 @@
       </c>
       <c r="J18" s="21" t="inlineStr">
         <is>
-          <t>J | 306呎 (1房)
+          <t>J | 305呎 (1房)
 $537万
-$17,539/呎
+$17,597/呎
 (25年-03月-25日)</t>
         </is>
       </c>
@@ -65954,9 +65954,9 @@
       </c>
       <c r="N18" s="21" t="inlineStr">
         <is>
-          <t>N | 285呎 (1房)
+          <t>N | 288呎 (1房)
 $549万
-$19,249/呎
+$19,049/呎
 (25年-06月-17日)</t>
         </is>
       </c>
@@ -65969,9 +65969,9 @@
       </c>
       <c r="B19" s="21" t="inlineStr">
         <is>
-          <t>A | 774呎 (3房)
+          <t>A | 771呎 (3房)
 $1851万
-$23,912/呎
+$24,005/呎
 (26年-04月-16日)</t>
         </is>
       </c>
@@ -66080,9 +66080,9 @@
       </c>
       <c r="B20" s="21" t="inlineStr">
         <is>
-          <t>A | 774呎 (3房)
+          <t>A | 771呎 (3房)
 $1888万
-$24,393/呎
+$24,488/呎
 (26年-05月-26日)</t>
         </is>
       </c>
@@ -66096,7 +66096,7 @@
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>C | 497呎 (2房)
+          <t>C | 498呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -66207,9 +66207,9 @@
       </c>
       <c r="D21" s="21" t="inlineStr">
         <is>
-          <t>C | 497呎 (2房)
+          <t>C | 498呎 (2房)
 $1143万
-$22,994/呎
+$22,948/呎
 (26年-06月-09日)</t>
         </is>
       </c>
@@ -66398,9 +66398,9 @@
       </c>
       <c r="N22" s="21" t="inlineStr">
         <is>
-          <t>N | 285呎 (1房)
+          <t>N | 288呎 (1房)
 $483万
-$16,961/呎
+$16,785/呎
 (24年-10月-03日)</t>
         </is>
       </c>
@@ -66429,9 +66429,9 @@
       </c>
       <c r="D23" s="21" t="inlineStr">
         <is>
-          <t>C | 497呎 (2房)
+          <t>C | 498呎 (2房)
 $1081万
-$21,746/呎
+$21,703/呎
 (26年-05月-15日)</t>
         </is>
       </c>
@@ -66588,9 +66588,9 @@
       </c>
       <c r="J24" s="21" t="inlineStr">
         <is>
-          <t>J | 306呎 (1房)
+          <t>J | 305呎 (1房)
 $522万
-$17,052/呎
+$17,108/呎
 (25年-03月-06日)</t>
         </is>
       </c>
@@ -66635,9 +66635,9 @@
       </c>
       <c r="B25" s="21" t="inlineStr">
         <is>
-          <t>A | 774呎 (3房)
+          <t>A | 771呎 (3房)
 $1759万
-$22,724/呎
+$22,812/呎
 (26年-03月-23日)</t>
         </is>
       </c>
@@ -66651,9 +66651,9 @@
       </c>
       <c r="D25" s="21" t="inlineStr">
         <is>
-          <t>C | 497呎 (2房)
+          <t>C | 498呎 (2房)
 $1071万
-$21,545/呎
+$21,502/呎
 (26年-05月-26日)</t>
         </is>
       </c>
@@ -66699,9 +66699,9 @@
       </c>
       <c r="J25" s="21" t="inlineStr">
         <is>
-          <t>J | 306呎 (1房)
+          <t>J | 305呎 (1房)
 $524万
-$17,131/呎
+$17,187/呎
 (25年-03月-24日)</t>
         </is>
       </c>
@@ -66857,9 +66857,9 @@
       </c>
       <c r="B27" s="21" t="inlineStr">
         <is>
-          <t>A | 774呎 (3房)
+          <t>A | 771呎 (3房)
 $1697万
-$21,922/呎
+$22,008/呎
 (26年-03月-05日)</t>
         </is>
       </c>
@@ -66937,9 +66937,9 @@
       </c>
       <c r="L27" s="21" t="inlineStr">
         <is>
-          <t>L | 429呎 (2房)
+          <t>L | 430呎 (2房)
 $861万
-$20,065/呎
+$20,019/呎
 (26年-03月-03日)</t>
         </is>
       </c>
@@ -66953,9 +66953,9 @@
       </c>
       <c r="N27" s="21" t="inlineStr">
         <is>
-          <t>N | 285呎 (1房)
+          <t>N | 288呎 (1房)
 $476万
-$16,702/呎
+$16,528/呎
 (24年-10月-03日)</t>
         </is>
       </c>
@@ -66984,9 +66984,9 @@
       </c>
       <c r="D28" s="21" t="inlineStr">
         <is>
-          <t>C | 497呎 (2房)
+          <t>C | 498呎 (2房)
 $1001万
-$20,137/呎
+$20,096/呎
 (26年-03月-06日)</t>
         </is>
       </c>
@@ -67032,9 +67032,9 @@
       </c>
       <c r="J28" s="21" t="inlineStr">
         <is>
-          <t>J | 306呎 (1房)
+          <t>J | 305呎 (1房)
 $592万
-$19,337/呎
+$19,400/呎
 (25年-10月-13日)</t>
         </is>
       </c>
@@ -67048,9 +67048,9 @@
       </c>
       <c r="L28" s="21" t="inlineStr">
         <is>
-          <t>L | 429呎 (2房)
+          <t>L | 430呎 (2房)
 $848万
-$19,767/呎
+$19,721/呎
 (23年-11月-20日)</t>
         </is>
       </c>
@@ -67143,9 +67143,9 @@
       </c>
       <c r="J29" s="21" t="inlineStr">
         <is>
-          <t>J | 306呎 (1房)
+          <t>J | 305呎 (1房)
 $514万
-$16,791/呎
+$16,846/呎
 (25年-03月-14日)</t>
         </is>
       </c>
@@ -67190,9 +67190,9 @@
       </c>
       <c r="B30" s="21" t="inlineStr">
         <is>
-          <t>A | 774呎 (3房)
+          <t>A | 771呎 (3房)
 $1661万
-$21,460/呎
+$21,543/呎
 (26年-01月-06日)</t>
         </is>
       </c>
@@ -67317,9 +67317,9 @@
       </c>
       <c r="D31" s="21" t="inlineStr">
         <is>
-          <t>C | 497呎 (2房)
+          <t>C | 498呎 (2房)
 $999万
-$20,097/呎
+$20,056/呎
 (26年-04月-01日)</t>
         </is>
       </c>
@@ -67412,9 +67412,9 @@
       </c>
       <c r="B32" s="21" t="inlineStr">
         <is>
-          <t>A | 774呎 (3房)
+          <t>A | 771呎 (3房)
 $1660万
-$21,444/呎
+$21,528/呎
 (26年-03月-10日)</t>
         </is>
       </c>
@@ -67428,9 +67428,9 @@
       </c>
       <c r="D32" s="21" t="inlineStr">
         <is>
-          <t>C | 497呎 (2房)
+          <t>C | 498呎 (2房)
 $974万
-$19,594/呎
+$19,554/呎
 (26年-02月-26日)</t>
         </is>
       </c>
@@ -67484,9 +67484,9 @@
       </c>
       <c r="K32" s="21" t="inlineStr">
         <is>
-          <t>K | 309呎 (1房)
+          <t>K | 308呎 (1房)
 $502万
-$16,246/呎
+$16,299/呎
 (24年-12月-30日)</t>
         </is>
       </c>
@@ -67508,9 +67508,9 @@
       </c>
       <c r="N32" s="21" t="inlineStr">
         <is>
-          <t>N | 285呎 (1房)
+          <t>N | 288呎 (1房)
 $467万
-$16,400/呎
+$16,229/呎
 (24年-09月-26日)</t>
         </is>
       </c>
@@ -67523,9 +67523,9 @@
       </c>
       <c r="B33" s="21" t="inlineStr">
         <is>
-          <t>A | 774呎 (3房)
+          <t>A | 771呎 (3房)
 $1681万
-$21,716/呎
+$21,800/呎
 (26年-04月-10日)</t>
         </is>
       </c>
@@ -67539,9 +67539,9 @@
       </c>
       <c r="D33" s="21" t="inlineStr">
         <is>
-          <t>C | 497呎 (2房)
+          <t>C | 498呎 (2房)
 $985万
-$19,815/呎
+$19,775/呎
 (26年-04月-15日)</t>
         </is>
       </c>
@@ -67634,9 +67634,9 @@
       </c>
       <c r="B34" s="21" t="inlineStr">
         <is>
-          <t>A | 774呎 (3房)
+          <t>A | 771呎 (3房)
 $1681万
-$21,716/呎
+$21,800/呎
 (26年-04月-08日)</t>
         </is>
       </c>
@@ -67650,9 +67650,9 @@
       </c>
       <c r="D34" s="21" t="inlineStr">
         <is>
-          <t>C | 497呎 (2房)
+          <t>C | 498呎 (2房)
 $978万
-$19,674/呎
+$19,635/呎
 (26年-04月-02日)</t>
         </is>
       </c>
@@ -68041,9 +68041,9 @@
       </c>
       <c r="J6" s="21" t="inlineStr">
         <is>
-          <t>J | 537呎 (2房)
+          <t>J | 538呎 (2房)
 $1454万
-$27,073/呎
+$27,022/呎
 (26年-06月-11日)</t>
         </is>
       </c>
@@ -68191,17 +68191,17 @@
       </c>
       <c r="I8" s="21" t="inlineStr">
         <is>
-          <t>H | 432呎 (2房)
+          <t>H | 431呎 (2房)
 $812万
-$18,789/呎
+$18,833/呎
 (26年-02月-24日)</t>
         </is>
       </c>
       <c r="J8" s="21" t="inlineStr">
         <is>
-          <t>J | 537呎 (2房)
+          <t>J | 538呎 (2房)
 $1148万
-$21,378/呎
+$21,338/呎
 (25年-08月-18日)</t>
         </is>
       </c>
@@ -68270,9 +68270,9 @@
       </c>
       <c r="I9" s="21" t="inlineStr">
         <is>
-          <t>H | 432呎 (2房)
+          <t>H | 431呎 (2房)
 $807万
-$18,688/呎
+$18,731/呎
 (26年-02月-09日)</t>
         </is>
       </c>
@@ -68349,9 +68349,9 @@
       </c>
       <c r="I10" s="21" t="inlineStr">
         <is>
-          <t>H | 432呎 (2房)
+          <t>H | 431呎 (2房)
 $806万
-$18,653/呎
+$18,696/呎
 (26年-02月-05日)</t>
         </is>
       </c>
@@ -68428,9 +68428,9 @@
       </c>
       <c r="I11" s="21" t="inlineStr">
         <is>
-          <t>H | 432呎 (2房)
+          <t>H | 431呎 (2房)
 $803万
-$18,590/呎
+$18,633/呎
 (26年-01月-15日)</t>
         </is>
       </c>
@@ -68507,17 +68507,17 @@
       </c>
       <c r="I12" s="21" t="inlineStr">
         <is>
-          <t>H | 432呎 (2房)
+          <t>H | 431呎 (2房)
 $757万
-$17,528/呎
+$17,568/呎
 (25年-03月-26日)</t>
         </is>
       </c>
       <c r="J12" s="21" t="inlineStr">
         <is>
-          <t>J | 537呎 (2房)
+          <t>J | 538呎 (2房)
 $1060万
-$19,739/呎
+$19,703/呎
 (25年-04月-25日)</t>
         </is>
       </c>
@@ -68981,9 +68981,9 @@
       </c>
       <c r="I18" s="21" t="inlineStr">
         <is>
-          <t>H | 432呎 (2房)
+          <t>H | 431呎 (2房)
 $781万
-$18,076/呎
+$18,118/呎
 (26年-01月-07日)</t>
         </is>
       </c>
@@ -69068,9 +69068,9 @@
       </c>
       <c r="J19" s="21" t="inlineStr">
         <is>
-          <t>J | 537呎 (2房)
+          <t>J | 538呎 (2房)
 $1026万
-$19,097/呎
+$19,061/呎
 (25年-03月-07日)</t>
         </is>
       </c>
@@ -69139,9 +69139,9 @@
       </c>
       <c r="I20" s="21" t="inlineStr">
         <is>
-          <t>H | 432呎 (2房)
+          <t>H | 431呎 (2房)
 $777万
-$17,981/呎
+$18,023/呎
 (25年-11月-24日)</t>
         </is>
       </c>
@@ -69455,9 +69455,9 @@
       </c>
       <c r="I24" s="21" t="inlineStr">
         <is>
-          <t>H | 432呎 (2房)
+          <t>H | 431呎 (2房)
 $714万
-$16,528/呎
+$16,566/呎
 (24年-11月-11日)</t>
         </is>
       </c>
@@ -69692,9 +69692,9 @@
       </c>
       <c r="I27" s="21" t="inlineStr">
         <is>
-          <t>H | 432呎 (2房)
+          <t>H | 431呎 (2房)
 $710万
-$16,433/呎
+$16,471/呎
 (25年-02月-07日)</t>
         </is>
       </c>
@@ -69779,9 +69779,9 @@
       </c>
       <c r="J28" s="21" t="inlineStr">
         <is>
-          <t>J | 537呎 (2房)
+          <t>J | 538呎 (2房)
 $962万
-$17,909/呎
+$17,875/呎
 (24年-11月-20日)</t>
         </is>
       </c>
@@ -69850,9 +69850,9 @@
       </c>
       <c r="I29" s="21" t="inlineStr">
         <is>
-          <t>H | 432呎 (2房)
+          <t>H | 431呎 (2房)
 $701万
-$16,222/呎
+$16,260/呎
 (24年-11月-12日)</t>
         </is>
       </c>
@@ -69929,9 +69929,9 @@
       </c>
       <c r="I30" s="21" t="inlineStr">
         <is>
-          <t>H | 432呎 (2房)
+          <t>H | 431呎 (2房)
 $699万
-$16,188/呎
+$16,225/呎
 (24年-10月-14日)</t>
         </is>
       </c>
@@ -70166,9 +70166,9 @@
       </c>
       <c r="I33" s="21" t="inlineStr">
         <is>
-          <t>H | 432呎 (2房)
+          <t>H | 431呎 (2房)
 $754万
-$17,461/呎
+$17,501/呎
 (26年-02月-20日)</t>
         </is>
       </c>
@@ -71099,9 +71099,9 @@
       </c>
       <c r="I11" s="20" t="inlineStr">
         <is>
-          <t>H | 306呎 (1房)
+          <t>H | 305呎 (1房)
 $905万
-$29,575/呎
+$29,672/呎
 (在售)</t>
         </is>
       </c>
@@ -71115,9 +71115,9 @@
       </c>
       <c r="K11" s="21" t="inlineStr">
         <is>
-          <t>K | 306呎 (1房)
+          <t>K | 305呎 (1房)
 $681万
-$22,248/呎
+$22,321/呎
 (26年-08月-26日)</t>
         </is>
       </c>
@@ -71218,9 +71218,9 @@
       </c>
       <c r="K12" s="21" t="inlineStr">
         <is>
-          <t>K | 306呎 (1房)
+          <t>K | 305呎 (1房)
 $673万
-$21,987/呎
+$22,059/呎
 (26年-08月-20日)</t>
         </is>
       </c>
@@ -71305,9 +71305,9 @@
       </c>
       <c r="I13" s="21" t="inlineStr">
         <is>
-          <t>H | 306呎 (1房)
+          <t>H | 305呎 (1房)
 $646万
-$21,098/呎
+$21,167/呎
 (26年-05月-22日)</t>
         </is>
       </c>
@@ -71321,17 +71321,17 @@
       </c>
       <c r="K13" s="21" t="inlineStr">
         <is>
-          <t>K | 306呎 (1房)
+          <t>K | 305呎 (1房)
 $647万
-$21,137/呎
+$21,207/呎
 (26年-05月-21日)</t>
         </is>
       </c>
       <c r="L13" s="21" t="inlineStr">
         <is>
-          <t>L | 429呎 (2房)
+          <t>L | 430呎 (2房)
 $936万
-$21,807/呎
+$21,756/呎
 (26年-05月-05日)</t>
         </is>
       </c>
@@ -71408,9 +71408,9 @@
       </c>
       <c r="I14" s="21" t="inlineStr">
         <is>
-          <t>H | 306呎 (1房)
+          <t>H | 305呎 (1房)
 $568万
-$18,562/呎
+$18,623/呎
 (25年-12月-24日)</t>
         </is>
       </c>
@@ -71424,17 +71424,17 @@
       </c>
       <c r="K14" s="21" t="inlineStr">
         <is>
-          <t>K | 306呎 (1房)
+          <t>K | 305呎 (1房)
 $639万
-$20,876/呎
+$20,944/呎
 (26年-04月-27日)</t>
         </is>
       </c>
       <c r="L14" s="21" t="inlineStr">
         <is>
-          <t>L | 429呎 (2房)
+          <t>L | 430呎 (2房)
 $925万
-$21,557/呎
+$21,507/呎
 (26年-04月-10日)</t>
         </is>
       </c>
@@ -71511,9 +71511,9 @@
       </c>
       <c r="I15" s="21" t="inlineStr">
         <is>
-          <t>H | 306呎 (1房)
+          <t>H | 305呎 (1房)
 $567万
-$18,520/呎
+$18,580/呎
 (25年-12月-31日)</t>
         </is>
       </c>
@@ -71527,17 +71527,17 @@
       </c>
       <c r="K15" s="21" t="inlineStr">
         <is>
-          <t>K | 306呎 (1房)
+          <t>K | 305呎 (1房)
 $629万
-$20,549/呎
+$20,616/呎
 (26年-03月-19日)</t>
         </is>
       </c>
       <c r="L15" s="21" t="inlineStr">
         <is>
-          <t>L | 429呎 (2房)
+          <t>L | 430呎 (2房)
 $909万
-$21,184/呎
+$21,135/呎
 (26年-04月-09日)</t>
         </is>
       </c>
@@ -71614,9 +71614,9 @@
       </c>
       <c r="I16" s="21" t="inlineStr">
         <is>
-          <t>H | 306呎 (1房)
+          <t>H | 305呎 (1房)
 $566万
-$18,480/呎
+$18,541/呎
 (25年-12月-09日)</t>
         </is>
       </c>
@@ -71630,17 +71630,17 @@
       </c>
       <c r="K16" s="21" t="inlineStr">
         <is>
-          <t>K | 306呎 (1房)
+          <t>K | 305呎 (1房)
 $602万
-$19,690/呎
+$19,754/呎
 (26年-03月-03日)</t>
         </is>
       </c>
       <c r="L16" s="21" t="inlineStr">
         <is>
-          <t>L | 429呎 (2房)
+          <t>L | 430呎 (2房)
 $882万
-$20,555/呎
+$20,507/呎
 (26年-03月-06日)</t>
         </is>
       </c>
@@ -71733,17 +71733,17 @@
       </c>
       <c r="K17" s="21" t="inlineStr">
         <is>
-          <t>K | 306呎 (1房)
+          <t>K | 305呎 (1房)
 $611万
-$19,961/呎
+$20,026/呎
 (26年-02月-26日)</t>
         </is>
       </c>
       <c r="L17" s="21" t="inlineStr">
         <is>
-          <t>L | 429呎 (2房)
+          <t>L | 430呎 (2房)
 $863万
-$20,112/呎
+$20,065/呎
 (26年-02月-11日)</t>
         </is>
       </c>
@@ -71836,17 +71836,17 @@
       </c>
       <c r="K18" s="21" t="inlineStr">
         <is>
-          <t>K | 306呎 (1房)
+          <t>K | 305呎 (1房)
 $598万
-$19,542/呎
+$19,607/呎
 (26年-03月-02日)</t>
         </is>
       </c>
       <c r="L18" s="21" t="inlineStr">
         <is>
-          <t>L | 429呎 (2房)
+          <t>L | 430呎 (2房)
 $837万
-$19,510/呎
+$19,465/呎
 (25年-12月-18日)</t>
         </is>
       </c>
@@ -71939,17 +71939,17 @@
       </c>
       <c r="K19" s="21" t="inlineStr">
         <is>
-          <t>K | 306呎 (1房)
+          <t>K | 305呎 (1房)
 $607万
-$19,830/呎
+$19,895/呎
 (26年-03月-09日)</t>
         </is>
       </c>
       <c r="L19" s="21" t="inlineStr">
         <is>
-          <t>L | 429呎 (2房)
+          <t>L | 430呎 (2房)
 $847万
-$19,739/呎
+$19,693/呎
 (26年-01月-13日)</t>
         </is>
       </c>
@@ -72042,9 +72042,9 @@
       </c>
       <c r="K20" s="21" t="inlineStr">
         <is>
-          <t>K | 306呎 (1房)
+          <t>K | 305呎 (1房)
 $572万
-$18,686/呎
+$18,748/呎
 (25年-12月-18日)</t>
         </is>
       </c>
@@ -72145,17 +72145,17 @@
       </c>
       <c r="K21" s="21" t="inlineStr">
         <is>
-          <t>K | 306呎 (1房)
+          <t>K | 305呎 (1房)
 $570万
-$18,621/呎
+$18,682/呎
 (26年-01月-05日)</t>
         </is>
       </c>
       <c r="L21" s="21" t="inlineStr">
         <is>
-          <t>L | 429呎 (2房)
+          <t>L | 430呎 (2房)
 $814万
-$18,979/呎
+$18,935/呎
 (25年-12月-03日)</t>
         </is>
       </c>
@@ -72351,17 +72351,17 @@
       </c>
       <c r="K23" s="21" t="inlineStr">
         <is>
-          <t>K | 306呎 (1房)
+          <t>K | 305呎 (1房)
 $566万
-$18,490/呎
+$18,551/呎
 (25年-12月-30日)</t>
         </is>
       </c>
       <c r="L23" s="21" t="inlineStr">
         <is>
-          <t>L | 429呎 (2房)
+          <t>L | 430呎 (2房)
 $809万
-$18,865/呎
+$18,821/呎
 (25年-12月-10日)</t>
         </is>
       </c>
@@ -72438,9 +72438,9 @@
       </c>
       <c r="I24" s="21" t="inlineStr">
         <is>
-          <t>H | 306呎 (1房)
+          <t>H | 305呎 (1房)
 $553万
-$18,065/呎
+$18,125/呎
 (25年-12月-15日)</t>
         </is>
       </c>
@@ -72454,9 +72454,9 @@
       </c>
       <c r="K24" s="21" t="inlineStr">
         <is>
-          <t>K | 306呎 (1房)
+          <t>K | 305呎 (1房)
 $564万
-$18,425/呎
+$18,485/呎
 (26年-01月-02日)</t>
         </is>
       </c>
@@ -72557,17 +72557,17 @@
       </c>
       <c r="K25" s="21" t="inlineStr">
         <is>
-          <t>K | 306呎 (1房)
+          <t>K | 305呎 (1房)
 $562万
-$18,359/呎
+$18,420/呎
 (26年-01月-14日)</t>
         </is>
       </c>
       <c r="L25" s="21" t="inlineStr">
         <is>
-          <t>L | 429呎 (2房)
+          <t>L | 430呎 (2房)
 $804万
-$18,748/呎
+$18,705/呎
 (25年-12月-08日)</t>
         </is>
       </c>
@@ -72660,9 +72660,9 @@
       </c>
       <c r="K26" s="21" t="inlineStr">
         <is>
-          <t>K | 306呎 (1房)
+          <t>K | 305呎 (1房)
 $560万
-$18,301/呎
+$18,361/呎
 (25年-12月-24日)</t>
         </is>
       </c>
@@ -72763,9 +72763,9 @@
       </c>
       <c r="K27" s="21" t="inlineStr">
         <is>
-          <t>K | 306呎 (1房)
+          <t>K | 305呎 (1房)
 $559万
-$18,268/呎
+$18,328/呎
 (25年-12月-09日)</t>
         </is>
       </c>
@@ -72866,9 +72866,9 @@
       </c>
       <c r="K28" s="21" t="inlineStr">
         <is>
-          <t>K | 306呎 (1房)
+          <t>K | 305呎 (1房)
 $549万
-$17,935/呎
+$17,993/呎
 (25年-12月-09日)</t>
         </is>
       </c>
@@ -72953,9 +72953,9 @@
       </c>
       <c r="I29" s="21" t="inlineStr">
         <is>
-          <t>H | 306呎 (1房)
+          <t>H | 305呎 (1房)
 $542万
-$17,709/呎
+$17,767/呎
 (25年-12月-10日)</t>
         </is>
       </c>
@@ -72969,9 +72969,9 @@
       </c>
       <c r="K29" s="21" t="inlineStr">
         <is>
-          <t>K | 306呎 (1房)
+          <t>K | 305呎 (1房)
 $546万
-$17,830/呎
+$17,889/呎
 (25年-12月-12日)</t>
         </is>
       </c>
@@ -73056,9 +73056,9 @@
       </c>
       <c r="I30" s="21" t="inlineStr">
         <is>
-          <t>H | 306呎 (1房)
+          <t>H | 305呎 (1房)
 $540万
-$17,663/呎
+$17,721/呎
 (25年-12月-16日)</t>
         </is>
       </c>
@@ -73175,9 +73175,9 @@
       </c>
       <c r="K31" s="21" t="inlineStr">
         <is>
-          <t>K | 306呎 (1房)
+          <t>K | 305呎 (1房)
 $534万
-$17,444/呎
+$17,502/呎
 (25年-12月-23日)</t>
         </is>
       </c>
@@ -73262,9 +73262,9 @@
       </c>
       <c r="I32" s="21" t="inlineStr">
         <is>
-          <t>H | 306呎 (1房)
+          <t>H | 305呎 (1房)
 $525万
-$17,157/呎
+$17,213/呎
 (25年-12月-03日)</t>
         </is>
       </c>
@@ -73278,9 +73278,9 @@
       </c>
       <c r="K32" s="21" t="inlineStr">
         <is>
-          <t>K | 306呎 (1房)
+          <t>K | 305呎 (1房)
 $526万
-$17,190/呎
+$17,246/呎
 (25年-12月-11日)</t>
         </is>
       </c>
@@ -73365,9 +73365,9 @@
       </c>
       <c r="I33" s="21" t="inlineStr">
         <is>
-          <t>H | 306呎 (1房)
+          <t>H | 305呎 (1房)
 $519万
-$16,954/呎
+$17,010/呎
 (25年-12月-05日)</t>
         </is>
       </c>
@@ -73420,17 +73420,17 @@
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>B | 445呎 (2房)
+          <t>B | 444呎 (2房)
 $1066万
-$23,946/呎
+$24,000/呎
 (26年-02月-23日)</t>
         </is>
       </c>
       <c r="D34" s="21" t="inlineStr">
         <is>
-          <t>C | 513呎 (2房)
+          <t>C | 514呎 (2房)
 $1313万
-$25,591/呎
+$25,541/呎
 (26年-04月-24日)</t>
         </is>
       </c>
@@ -73461,9 +73461,9 @@
       </c>
       <c r="I34" s="21" t="inlineStr">
         <is>
-          <t>H | 306呎 (1房)
+          <t>H | 305呎 (1房)
 $519万
-$16,954/呎
+$17,010/呎
 (25年-12月-17日)</t>
         </is>
       </c>
@@ -73477,17 +73477,17 @@
       </c>
       <c r="K34" s="21" t="inlineStr">
         <is>
-          <t>K | 306呎 (1房)
+          <t>K | 305呎 (1房)
 $519万
-$16,954/呎
+$17,010/呎
 (25年-12月-17日)</t>
         </is>
       </c>
       <c r="L34" s="21" t="inlineStr">
         <is>
-          <t>L | 429呎 (2房)
+          <t>L | 430呎 (2房)
 $710万
-$16,550/呎
+$16,512/呎
 (25年-12月-31日)</t>
         </is>
       </c>
